--- a/research/traditional_assets/database/data/pakistan/pakistan_hospitals_healthcare_facilities.xlsx
+++ b/research/traditional_assets/database/data/pakistan/pakistan_hospitals_healthcare_facilities.xlsx
@@ -1278,7 +1278,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1415,22 +1415,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.1381617399976413</v>
+        <v>0.1377930209516482</v>
       </c>
       <c r="C2">
-        <v>96.82914369139729</v>
+        <v>96.22552643562074</v>
       </c>
       <c r="D2">
-        <v>86.96914369139729</v>
+        <v>87.31772643562074</v>
       </c>
       <c r="E2">
-        <v>-5.22</v>
+        <v>-4.267799999999999</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>0.9522</v>
       </c>
       <c r="G2">
         <v>9.859999999999999</v>
@@ -1451,28 +1451,28 @@
         <v>10.5</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.04789566</v>
       </c>
       <c r="N2">
-        <v>10.5</v>
+        <v>10.45210434</v>
       </c>
       <c r="O2">
-        <v>3.045</v>
+        <v>3.0311102586</v>
       </c>
       <c r="P2">
-        <v>7.455</v>
+        <v>7.4209940814</v>
       </c>
       <c r="Q2">
-        <v>11.355</v>
+        <v>11.3209940814</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.1381617399976413</v>
+        <v>0.1388241322743921</v>
       </c>
       <c r="T2">
-        <v>0.5648729042001043</v>
+        <v>0.5689240129069939</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1489,7 +1489,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>219.2265436993665</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1497,22 +1497,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.1377930209516482</v>
+        <v>0.137424301905655</v>
       </c>
       <c r="C3">
-        <v>96.22552643562074</v>
+        <v>95.62471474767345</v>
       </c>
       <c r="D3">
-        <v>87.31772643562074</v>
+        <v>87.66911474767345</v>
       </c>
       <c r="E3">
-        <v>-4.267799999999999</v>
+        <v>-3.3156</v>
       </c>
       <c r="F3">
-        <v>0.9522</v>
+        <v>1.9044</v>
       </c>
       <c r="G3">
         <v>9.859999999999999</v>
@@ -1533,28 +1533,28 @@
         <v>10.5</v>
       </c>
       <c r="M3">
-        <v>0.04789566</v>
+        <v>0.09579132</v>
       </c>
       <c r="N3">
-        <v>10.45210434</v>
+        <v>10.40420868</v>
       </c>
       <c r="O3">
-        <v>3.0311102586</v>
+        <v>3.0172205172</v>
       </c>
       <c r="P3">
-        <v>7.4209940814</v>
+        <v>7.3869881628</v>
       </c>
       <c r="Q3">
-        <v>11.3209940814</v>
+        <v>11.2869881628</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.1388241322743921</v>
+        <v>0.1395000427608724</v>
       </c>
       <c r="T3">
-        <v>0.5689240129069939</v>
+        <v>0.5730577973017793</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>219.2265436993665</v>
+        <v>109.6132718496832</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1579,22 +1579,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.137424301905655</v>
+        <v>0.1370555828596619</v>
       </c>
       <c r="C4">
-        <v>95.62471474767345</v>
+        <v>95.02674263532539</v>
       </c>
       <c r="D4">
-        <v>87.66911474767345</v>
+        <v>88.02334263532539</v>
       </c>
       <c r="E4">
-        <v>-3.3156</v>
+        <v>-2.3634</v>
       </c>
       <c r="F4">
-        <v>1.9044</v>
+        <v>2.8566</v>
       </c>
       <c r="G4">
         <v>9.859999999999999</v>
@@ -1615,28 +1615,28 @@
         <v>10.5</v>
       </c>
       <c r="M4">
-        <v>0.09579132</v>
+        <v>0.14368698</v>
       </c>
       <c r="N4">
-        <v>10.40420868</v>
+        <v>10.35631302</v>
       </c>
       <c r="O4">
-        <v>3.0172205172</v>
+        <v>3.0033307758</v>
       </c>
       <c r="P4">
-        <v>7.3869881628</v>
+        <v>7.3529822442</v>
       </c>
       <c r="Q4">
-        <v>11.2869881628</v>
+        <v>11.2529822442</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.1395000427608724</v>
+        <v>0.1401898895460431</v>
       </c>
       <c r="T4">
-        <v>0.5730577973017793</v>
+        <v>0.5772768143644984</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>109.6132718496832</v>
+        <v>73.07551456645551</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1661,22 +1661,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.1370555828596619</v>
+        <v>0.1366868638136687</v>
       </c>
       <c r="C5">
-        <v>95.02674263532539</v>
+        <v>94.43164465821143</v>
       </c>
       <c r="D5">
-        <v>88.02334263532539</v>
+        <v>88.38044465821143</v>
       </c>
       <c r="E5">
-        <v>-2.3634</v>
+        <v>-1.4112</v>
       </c>
       <c r="F5">
-        <v>2.8566</v>
+        <v>3.8088</v>
       </c>
       <c r="G5">
         <v>9.859999999999999</v>
@@ -1697,28 +1697,28 @@
         <v>10.5</v>
       </c>
       <c r="M5">
-        <v>0.14368698</v>
+        <v>0.19158264</v>
       </c>
       <c r="N5">
-        <v>10.35631302</v>
+        <v>10.30841736</v>
       </c>
       <c r="O5">
-        <v>3.0033307758</v>
+        <v>2.9894410344</v>
       </c>
       <c r="P5">
-        <v>7.3529822442</v>
+        <v>7.3189763256</v>
       </c>
       <c r="Q5">
-        <v>11.2529822442</v>
+        <v>11.2189763256</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.1401898895460431</v>
+        <v>0.1408941081392382</v>
       </c>
       <c r="T5">
-        <v>0.5772768143644984</v>
+        <v>0.5815837276160241</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>73.07551456645551</v>
+        <v>54.80663592484162</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.1366868638136687</v>
+        <v>0.1363181447676755</v>
       </c>
       <c r="C6">
-        <v>94.43164465821143</v>
+        <v>93.83945593907082</v>
       </c>
       <c r="D6">
-        <v>88.38044465821143</v>
+        <v>88.74045593907081</v>
       </c>
       <c r="E6">
-        <v>-1.4112</v>
+        <v>-0.4589999999999996</v>
       </c>
       <c r="F6">
-        <v>3.8088</v>
+        <v>4.761</v>
       </c>
       <c r="G6">
         <v>9.859999999999999</v>
@@ -1779,28 +1779,28 @@
         <v>10.5</v>
       </c>
       <c r="M6">
-        <v>0.19158264</v>
+        <v>0.2394783</v>
       </c>
       <c r="N6">
-        <v>10.30841736</v>
+        <v>10.2605217</v>
       </c>
       <c r="O6">
-        <v>2.9894410344</v>
+        <v>2.975551293</v>
       </c>
       <c r="P6">
-        <v>7.3189763256</v>
+        <v>7.284970407</v>
       </c>
       <c r="Q6">
-        <v>11.2189763256</v>
+        <v>11.184970407</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.1408941081392382</v>
+        <v>0.1416131523870268</v>
       </c>
       <c r="T6">
-        <v>0.5815837276160241</v>
+        <v>0.5859813127254766</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>54.80663592484162</v>
+        <v>43.8453087398733</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1825,22 +1825,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.1363181447676755</v>
+        <v>0.1359494257216824</v>
       </c>
       <c r="C7">
-        <v>93.83945593907082</v>
+        <v>93.25021217526324</v>
       </c>
       <c r="D7">
-        <v>88.74045593907081</v>
+        <v>89.10341217526324</v>
       </c>
       <c r="E7">
-        <v>-0.4589999999999996</v>
+        <v>0.4932000000000007</v>
       </c>
       <c r="F7">
-        <v>4.761</v>
+        <v>5.713200000000001</v>
       </c>
       <c r="G7">
         <v>9.859999999999999</v>
@@ -1861,28 +1861,28 @@
         <v>10.5</v>
       </c>
       <c r="M7">
-        <v>0.2394783</v>
+        <v>0.28737396</v>
       </c>
       <c r="N7">
-        <v>10.2605217</v>
+        <v>10.21262604</v>
       </c>
       <c r="O7">
-        <v>2.975551293</v>
+        <v>2.9616615516</v>
       </c>
       <c r="P7">
-        <v>7.284970407</v>
+        <v>7.2509644884</v>
       </c>
       <c r="Q7">
-        <v>11.184970407</v>
+        <v>11.1509644884</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1416131523870268</v>
+        <v>0.1423474954485983</v>
       </c>
       <c r="T7">
-        <v>0.5859813127254766</v>
+        <v>0.5904724634755558</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1899,7 +1899,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>43.8453087398733</v>
+        <v>36.53775728322775</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1907,22 +1907,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.1359494257216824</v>
+        <v>0.1355807066756892</v>
       </c>
       <c r="C8">
-        <v>93.25021217526324</v>
+        <v>92.66394965056823</v>
       </c>
       <c r="D8">
-        <v>89.10341217526324</v>
+        <v>89.46934965056823</v>
       </c>
       <c r="E8">
-        <v>0.4931999999999999</v>
+        <v>1.445399999999999</v>
       </c>
       <c r="F8">
-        <v>5.7132</v>
+        <v>6.665399999999999</v>
       </c>
       <c r="G8">
         <v>9.859999999999999</v>
@@ -1943,28 +1943,28 @@
         <v>10.5</v>
       </c>
       <c r="M8">
-        <v>0.28737396</v>
+        <v>0.3352696199999999</v>
       </c>
       <c r="N8">
-        <v>10.21262604</v>
+        <v>10.16473038</v>
       </c>
       <c r="O8">
-        <v>2.9616615516</v>
+        <v>2.9477718102</v>
       </c>
       <c r="P8">
-        <v>7.2509644884</v>
+        <v>7.2169585698</v>
       </c>
       <c r="Q8">
-        <v>11.1509644884</v>
+        <v>11.1169585698</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1423474954485983</v>
+        <v>0.1430976308340744</v>
       </c>
       <c r="T8">
-        <v>0.5904724634755558</v>
+        <v>0.5950601981127335</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1981,7 +1981,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>36.53775728322775</v>
+        <v>31.31807767133808</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1989,22 +1989,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.1355807066756892</v>
+        <v>0.135211987629696</v>
       </c>
       <c r="C9">
-        <v>92.66394965056827</v>
+        <v>92.0807052472765</v>
       </c>
       <c r="D9">
-        <v>89.46934965056828</v>
+        <v>89.83830524727649</v>
       </c>
       <c r="E9">
-        <v>1.445400000000001</v>
+        <v>2.397600000000001</v>
       </c>
       <c r="F9">
-        <v>6.665400000000001</v>
+        <v>7.6176</v>
       </c>
       <c r="G9">
         <v>9.859999999999999</v>
@@ -2025,28 +2025,28 @@
         <v>10.5</v>
       </c>
       <c r="M9">
-        <v>0.33526962</v>
+        <v>0.38316528</v>
       </c>
       <c r="N9">
-        <v>10.16473038</v>
+        <v>10.11683472</v>
       </c>
       <c r="O9">
-        <v>2.9477718102</v>
+        <v>2.9338820688</v>
       </c>
       <c r="P9">
-        <v>7.2169585698</v>
+        <v>7.182952651200001</v>
       </c>
       <c r="Q9">
-        <v>11.1169585698</v>
+        <v>11.0829526512</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1430976308340744</v>
+        <v>0.1438640735105391</v>
       </c>
       <c r="T9">
-        <v>0.5950601981127335</v>
+        <v>0.5997476661115889</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>31.31807767133807</v>
+        <v>27.40331796242081</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2071,22 +2071,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.135211987629696</v>
+        <v>0.1348432685837029</v>
       </c>
       <c r="C10">
-        <v>92.0807052472765</v>
+        <v>91.50051645858196</v>
       </c>
       <c r="D10">
-        <v>89.83830524727649</v>
+        <v>90.21031645858196</v>
       </c>
       <c r="E10">
-        <v>2.397600000000001</v>
+        <v>3.349799999999999</v>
       </c>
       <c r="F10">
-        <v>7.6176</v>
+        <v>8.569799999999999</v>
       </c>
       <c r="G10">
         <v>9.859999999999999</v>
@@ -2107,28 +2107,28 @@
         <v>10.5</v>
       </c>
       <c r="M10">
-        <v>0.38316528</v>
+        <v>0.4310609399999999</v>
       </c>
       <c r="N10">
-        <v>10.11683472</v>
+        <v>10.06893906</v>
       </c>
       <c r="O10">
-        <v>2.9338820688</v>
+        <v>2.9199923274</v>
       </c>
       <c r="P10">
-        <v>7.182952651200001</v>
+        <v>7.148946732600001</v>
       </c>
       <c r="Q10">
-        <v>11.0829526512</v>
+        <v>11.0489467326</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1438640735105391</v>
+        <v>0.1446473610809922</v>
       </c>
       <c r="T10">
-        <v>0.5997476661115889</v>
+        <v>0.6045381553851445</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2145,7 +2145,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>27.40331796242081</v>
+        <v>24.35850485548517</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2153,22 +2153,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.1348432685837029</v>
+        <v>0.1344745495377097</v>
       </c>
       <c r="C11">
-        <v>91.50051645858196</v>
+        <v>90.92342140128258</v>
       </c>
       <c r="D11">
-        <v>90.21031645858196</v>
+        <v>90.58542140128259</v>
       </c>
       <c r="E11">
-        <v>3.349799999999999</v>
+        <v>4.301999999999999</v>
       </c>
       <c r="F11">
-        <v>8.569799999999999</v>
+        <v>9.521999999999998</v>
       </c>
       <c r="G11">
         <v>9.859999999999999</v>
@@ -2189,28 +2189,28 @@
         <v>10.5</v>
       </c>
       <c r="M11">
-        <v>0.4310609399999999</v>
+        <v>0.4789565999999999</v>
       </c>
       <c r="N11">
-        <v>10.06893906</v>
+        <v>10.0210434</v>
       </c>
       <c r="O11">
-        <v>2.9199923274</v>
+        <v>2.906102586</v>
       </c>
       <c r="P11">
-        <v>7.148946732600001</v>
+        <v>7.114940814000001</v>
       </c>
       <c r="Q11">
-        <v>11.0489467326</v>
+        <v>11.014940814</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1446473610809922</v>
+        <v>0.1454480550418997</v>
       </c>
       <c r="T11">
-        <v>0.6045381553851445</v>
+        <v>0.6094350999758902</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2227,7 +2227,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>24.35850485548517</v>
+        <v>21.92265436993666</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2235,22 +2235,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.1344745495377097</v>
+        <v>0.1341058304917166</v>
       </c>
       <c r="C12">
-        <v>90.92342140128258</v>
+        <v>90.34945882879992</v>
       </c>
       <c r="D12">
-        <v>90.58542140128259</v>
+        <v>90.96365882879992</v>
       </c>
       <c r="E12">
-        <v>4.302</v>
+        <v>5.2542</v>
       </c>
       <c r="F12">
-        <v>9.522</v>
+        <v>10.4742</v>
       </c>
       <c r="G12">
         <v>9.859999999999999</v>
@@ -2271,28 +2271,28 @@
         <v>10.5</v>
       </c>
       <c r="M12">
-        <v>0.4789566</v>
+        <v>0.52685226</v>
       </c>
       <c r="N12">
-        <v>10.0210434</v>
+        <v>9.97314774</v>
       </c>
       <c r="O12">
-        <v>2.906102586</v>
+        <v>2.8922128446</v>
       </c>
       <c r="P12">
-        <v>7.114940814000001</v>
+        <v>7.0809348954</v>
       </c>
       <c r="Q12">
-        <v>11.014940814</v>
+        <v>10.9809348954</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1454480550418997</v>
+        <v>0.1462667421255242</v>
       </c>
       <c r="T12">
-        <v>0.6094350999758902</v>
+        <v>0.6144420882653044</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2309,7 +2309,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>21.92265436993665</v>
+        <v>19.9296857908515</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2317,22 +2317,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.1341058304917166</v>
+        <v>0.1337371114457234</v>
       </c>
       <c r="C13">
-        <v>90.34945882879992</v>
+        <v>89.77866814452558</v>
       </c>
       <c r="D13">
-        <v>90.96365882879992</v>
+        <v>91.34506814452558</v>
       </c>
       <c r="E13">
-        <v>5.2542</v>
+        <v>6.206399999999999</v>
       </c>
       <c r="F13">
-        <v>10.4742</v>
+        <v>11.4264</v>
       </c>
       <c r="G13">
         <v>9.859999999999999</v>
@@ -2353,28 +2353,28 @@
         <v>10.5</v>
       </c>
       <c r="M13">
-        <v>0.52685226</v>
+        <v>0.57474792</v>
       </c>
       <c r="N13">
-        <v>9.97314774</v>
+        <v>9.92525208</v>
       </c>
       <c r="O13">
-        <v>2.8922128446</v>
+        <v>2.8783231032</v>
       </c>
       <c r="P13">
-        <v>7.0809348954</v>
+        <v>7.0469289768</v>
       </c>
       <c r="Q13">
-        <v>10.9809348954</v>
+        <v>10.9469289768</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1462667421255242</v>
+        <v>0.1471040357337766</v>
       </c>
       <c r="T13">
-        <v>0.6144420882653044</v>
+        <v>0.6195628717431143</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2391,7 +2391,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>19.9296857908515</v>
+        <v>18.26887864161387</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2399,22 +2399,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.1337371114457234</v>
+        <v>0.1333683923997302</v>
       </c>
       <c r="C14">
-        <v>89.77866814452558</v>
+        <v>89.21108941550523</v>
       </c>
       <c r="D14">
-        <v>91.34506814452558</v>
+        <v>91.72968941550523</v>
       </c>
       <c r="E14">
-        <v>6.206399999999999</v>
+        <v>7.158600000000001</v>
       </c>
       <c r="F14">
-        <v>11.4264</v>
+        <v>12.3786</v>
       </c>
       <c r="G14">
         <v>9.859999999999999</v>
@@ -2435,28 +2435,28 @@
         <v>10.5</v>
       </c>
       <c r="M14">
-        <v>0.57474792</v>
+        <v>0.62264358</v>
       </c>
       <c r="N14">
-        <v>9.92525208</v>
+        <v>9.87735642</v>
       </c>
       <c r="O14">
-        <v>2.8783231032</v>
+        <v>2.8644333618</v>
       </c>
       <c r="P14">
-        <v>7.0469289768</v>
+        <v>7.0129230582</v>
       </c>
       <c r="Q14">
-        <v>10.9469289768</v>
+        <v>10.9129230582</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1471040357337766</v>
+        <v>0.1479605774709543</v>
       </c>
       <c r="T14">
-        <v>0.6195628717431143</v>
+        <v>0.6248013743813338</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2473,7 +2473,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>18.26887864161387</v>
+        <v>16.86358028456665</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2481,22 +2481,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.1333683923997302</v>
+        <v>0.1329996733537371</v>
       </c>
       <c r="C15">
-        <v>89.21108941550523</v>
+        <v>88.6467633864699</v>
       </c>
       <c r="D15">
-        <v>91.72968941550523</v>
+        <v>92.1175633864699</v>
       </c>
       <c r="E15">
-        <v>7.158600000000001</v>
+        <v>8.110800000000001</v>
       </c>
       <c r="F15">
-        <v>12.3786</v>
+        <v>13.3308</v>
       </c>
       <c r="G15">
         <v>9.859999999999999</v>
@@ -2517,28 +2517,28 @@
         <v>10.5</v>
       </c>
       <c r="M15">
-        <v>0.62264358</v>
+        <v>0.6705392400000001</v>
       </c>
       <c r="N15">
-        <v>9.87735642</v>
+        <v>9.82946076</v>
       </c>
       <c r="O15">
-        <v>2.8644333618</v>
+        <v>2.8505436204</v>
       </c>
       <c r="P15">
-        <v>7.0129230582</v>
+        <v>6.9789171396</v>
       </c>
       <c r="Q15">
-        <v>10.9129230582</v>
+        <v>10.8789171396</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1479605774709543</v>
+        <v>0.1488370387834152</v>
       </c>
       <c r="T15">
-        <v>0.6248013743813338</v>
+        <v>0.6301617026623023</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>16.86358028456665</v>
+        <v>15.65903883566903</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2563,22 +2563,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.1329996733537371</v>
+        <v>0.1326309543077439</v>
       </c>
       <c r="C16">
-        <v>88.6467633864699</v>
+        <v>88.08573149422432</v>
       </c>
       <c r="D16">
-        <v>92.1175633864699</v>
+        <v>92.50873149422432</v>
       </c>
       <c r="E16">
-        <v>8.110800000000001</v>
+        <v>9.063000000000002</v>
       </c>
       <c r="F16">
-        <v>13.3308</v>
+        <v>14.283</v>
       </c>
       <c r="G16">
         <v>9.859999999999999</v>
@@ -2599,28 +2599,28 @@
         <v>10.5</v>
       </c>
       <c r="M16">
-        <v>0.6705392400000001</v>
+        <v>0.7184349</v>
       </c>
       <c r="N16">
-        <v>9.82946076</v>
+        <v>9.7815651</v>
       </c>
       <c r="O16">
-        <v>2.8505436204</v>
+        <v>2.836653879</v>
       </c>
       <c r="P16">
-        <v>6.9789171396</v>
+        <v>6.944911221</v>
       </c>
       <c r="Q16">
-        <v>10.8789171396</v>
+        <v>10.844911221</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1488370387834152</v>
+        <v>0.1497341227149928</v>
       </c>
       <c r="T16">
-        <v>0.6301617026623023</v>
+        <v>0.6356481563145879</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2637,7 +2637,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>15.65903883566903</v>
+        <v>14.6151029132911</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2645,22 +2645,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.1326309543077439</v>
+        <v>0.1322622352617508</v>
       </c>
       <c r="C17">
-        <v>88.08573149422432</v>
+        <v>87.52803588240401</v>
       </c>
       <c r="D17">
-        <v>92.50873149422432</v>
+        <v>92.90323588240402</v>
       </c>
       <c r="E17">
-        <v>9.062999999999999</v>
+        <v>10.0152</v>
       </c>
       <c r="F17">
-        <v>14.283</v>
+        <v>15.2352</v>
       </c>
       <c r="G17">
         <v>9.859999999999999</v>
@@ -2681,28 +2681,28 @@
         <v>10.5</v>
       </c>
       <c r="M17">
-        <v>0.7184349</v>
+        <v>0.76633056</v>
       </c>
       <c r="N17">
-        <v>9.7815651</v>
+        <v>9.73366944</v>
       </c>
       <c r="O17">
-        <v>2.836653879</v>
+        <v>2.8227641376</v>
       </c>
       <c r="P17">
-        <v>6.944911221</v>
+        <v>6.9109053024</v>
       </c>
       <c r="Q17">
-        <v>10.844911221</v>
+        <v>10.8109053024</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1497341227149928</v>
+        <v>0.1506525657877985</v>
       </c>
       <c r="T17">
-        <v>0.6356481563145879</v>
+        <v>0.6412652398157374</v>
       </c>
       <c r="U17">
         <v>0.0503</v>
@@ -2719,7 +2719,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>14.6151029132911</v>
+        <v>13.70165898121041</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2727,22 +2727,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.1322622352617508</v>
+        <v>0.1318935162157576</v>
       </c>
       <c r="C18">
-        <v>87.52803588240401</v>
+        <v>86.97371941661112</v>
       </c>
       <c r="D18">
-        <v>92.90323588240402</v>
+        <v>93.30111941661112</v>
       </c>
       <c r="E18">
-        <v>10.0152</v>
+        <v>10.9674</v>
       </c>
       <c r="F18">
-        <v>15.2352</v>
+        <v>16.1874</v>
       </c>
       <c r="G18">
         <v>9.859999999999999</v>
@@ -2763,28 +2763,28 @@
         <v>10.5</v>
       </c>
       <c r="M18">
-        <v>0.76633056</v>
+        <v>0.81422622</v>
       </c>
       <c r="N18">
-        <v>9.73366944</v>
+        <v>9.68577378</v>
       </c>
       <c r="O18">
-        <v>2.8227641376</v>
+        <v>2.8088743962</v>
       </c>
       <c r="P18">
-        <v>6.9109053024</v>
+        <v>6.8768993838</v>
       </c>
       <c r="Q18">
-        <v>10.8109053024</v>
+        <v>10.7768993838</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1506525657877985</v>
+        <v>0.1515931400189851</v>
       </c>
       <c r="T18">
-        <v>0.6412652398157374</v>
+        <v>0.6470176747265531</v>
       </c>
       <c r="U18">
         <v>0.0503</v>
@@ -2801,7 +2801,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>13.70165898121041</v>
+        <v>12.89567904113921</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.1318935162157576</v>
+        <v>0.1317164971697644</v>
       </c>
       <c r="C19">
-        <v>86.97371941661112</v>
+        <v>86.2137534542324</v>
       </c>
       <c r="D19">
-        <v>93.30111941661112</v>
+        <v>93.49335345423241</v>
       </c>
       <c r="E19">
-        <v>10.9674</v>
+        <v>11.9196</v>
       </c>
       <c r="F19">
-        <v>16.1874</v>
+        <v>17.1396</v>
       </c>
       <c r="G19">
         <v>9.859999999999999</v>
@@ -2845,45 +2845,45 @@
         <v>10.5</v>
       </c>
       <c r="M19">
-        <v>0.81422622</v>
+        <v>0.8878312800000001</v>
       </c>
       <c r="N19">
-        <v>9.68577378</v>
+        <v>9.61216872</v>
       </c>
       <c r="O19">
-        <v>2.8088743962</v>
+        <v>2.7875289288</v>
       </c>
       <c r="P19">
-        <v>6.8768993838</v>
+        <v>6.8246397912</v>
       </c>
       <c r="Q19">
-        <v>10.7768993838</v>
+        <v>10.7246397912</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1515931400189851</v>
+        <v>0.1525566550850786</v>
       </c>
       <c r="T19">
-        <v>0.6470176747265531</v>
+        <v>0.6529104129278765</v>
       </c>
       <c r="U19">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V19">
         <v>0.29</v>
       </c>
       <c r="W19">
-        <v>0.03571299999999999</v>
+        <v>0.036778</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y19">
-        <v>12.89567904113921</v>
+        <v>11.82657137288517</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2891,22 +2891,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.1317164971697644</v>
+        <v>0.1313584281237713</v>
       </c>
       <c r="C20">
-        <v>86.21375345423237</v>
+        <v>85.65283081418607</v>
       </c>
       <c r="D20">
-        <v>93.49335345423238</v>
+        <v>93.88463081418608</v>
       </c>
       <c r="E20">
-        <v>11.9196</v>
+        <v>12.8718</v>
       </c>
       <c r="F20">
-        <v>17.1396</v>
+        <v>18.0918</v>
       </c>
       <c r="G20">
         <v>9.859999999999999</v>
@@ -2927,28 +2927,28 @@
         <v>10.5</v>
       </c>
       <c r="M20">
-        <v>0.8878312799999999</v>
+        <v>0.9371552399999999</v>
       </c>
       <c r="N20">
-        <v>9.61216872</v>
+        <v>9.562844760000001</v>
       </c>
       <c r="O20">
-        <v>2.7875289288</v>
+        <v>2.7732249804</v>
       </c>
       <c r="P20">
-        <v>6.8246397912</v>
+        <v>6.789619779600001</v>
       </c>
       <c r="Q20">
-        <v>10.7246397912</v>
+        <v>10.6896197796</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1525566550850786</v>
+        <v>0.1535439606466312</v>
       </c>
       <c r="T20">
-        <v>0.6529104129278765</v>
+        <v>0.6589486508378747</v>
       </c>
       <c r="U20">
         <v>0.0518</v>
@@ -2965,7 +2965,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>11.82657137288517</v>
+        <v>11.20412024799648</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2973,22 +2973,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.1313584281237713</v>
+        <v>0.1310003590777781</v>
       </c>
       <c r="C21">
-        <v>85.65283081418607</v>
+        <v>85.09519699387045</v>
       </c>
       <c r="D21">
-        <v>93.88463081418608</v>
+        <v>94.27919699387044</v>
       </c>
       <c r="E21">
-        <v>12.8718</v>
+        <v>13.824</v>
       </c>
       <c r="F21">
-        <v>18.0918</v>
+        <v>19.044</v>
       </c>
       <c r="G21">
         <v>9.859999999999999</v>
@@ -3009,28 +3009,28 @@
         <v>10.5</v>
       </c>
       <c r="M21">
-        <v>0.9371552399999999</v>
+        <v>0.9864792</v>
       </c>
       <c r="N21">
-        <v>9.562844760000001</v>
+        <v>9.5135208</v>
       </c>
       <c r="O21">
-        <v>2.7732249804</v>
+        <v>2.758921032</v>
       </c>
       <c r="P21">
-        <v>6.789619779600001</v>
+        <v>6.754599768</v>
       </c>
       <c r="Q21">
-        <v>10.6896197796</v>
+        <v>10.654599768</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1535439606466312</v>
+        <v>0.1545559488472227</v>
       </c>
       <c r="T21">
-        <v>0.6589486508378747</v>
+        <v>0.6651378446956228</v>
       </c>
       <c r="U21">
         <v>0.0518</v>
@@ -3047,7 +3047,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>11.20412024799648</v>
+        <v>10.64391423559666</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3055,22 +3055,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.1310003590777781</v>
+        <v>0.130642290031785</v>
       </c>
       <c r="C22">
-        <v>85.09519699387045</v>
+        <v>84.5408936337649</v>
       </c>
       <c r="D22">
-        <v>94.27919699387044</v>
+        <v>94.6770936337649</v>
       </c>
       <c r="E22">
-        <v>13.824</v>
+        <v>14.7762</v>
       </c>
       <c r="F22">
-        <v>19.044</v>
+        <v>19.9962</v>
       </c>
       <c r="G22">
         <v>9.859999999999999</v>
@@ -3091,28 +3091,28 @@
         <v>10.5</v>
       </c>
       <c r="M22">
-        <v>0.9864792</v>
+        <v>1.03580316</v>
       </c>
       <c r="N22">
-        <v>9.5135208</v>
+        <v>9.46419684</v>
       </c>
       <c r="O22">
-        <v>2.758921032</v>
+        <v>2.7446170836</v>
       </c>
       <c r="P22">
-        <v>6.754599768</v>
+        <v>6.7195797564</v>
       </c>
       <c r="Q22">
-        <v>10.654599768</v>
+        <v>10.6195797564</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1545559488472227</v>
+        <v>0.1555935570022594</v>
       </c>
       <c r="T22">
-        <v>0.6651378446956228</v>
+        <v>0.6714837270054657</v>
       </c>
       <c r="U22">
         <v>0.0518</v>
@@ -3129,7 +3129,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>10.64391423559666</v>
+        <v>10.13706117675872</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3137,22 +3137,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.130642290031785</v>
+        <v>0.1305497609857918</v>
       </c>
       <c r="C23">
-        <v>84.5408936337649</v>
+        <v>83.69206125450432</v>
       </c>
       <c r="D23">
-        <v>94.6770936337649</v>
+        <v>94.78046125450433</v>
       </c>
       <c r="E23">
-        <v>14.7762</v>
+        <v>15.7284</v>
       </c>
       <c r="F23">
-        <v>19.9962</v>
+        <v>20.9484</v>
       </c>
       <c r="G23">
         <v>9.859999999999999</v>
@@ -3173,45 +3173,45 @@
         <v>10.5</v>
       </c>
       <c r="M23">
-        <v>1.03580316</v>
+        <v>1.1207394</v>
       </c>
       <c r="N23">
-        <v>9.46419684</v>
+        <v>9.3792606</v>
       </c>
       <c r="O23">
-        <v>2.7446170836</v>
+        <v>2.719985574</v>
       </c>
       <c r="P23">
-        <v>6.7195797564</v>
+        <v>6.659275026</v>
       </c>
       <c r="Q23">
-        <v>10.6195797564</v>
+        <v>10.559275026</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1555935570022594</v>
+        <v>0.1566577704946049</v>
       </c>
       <c r="T23">
-        <v>0.6714837270054657</v>
+        <v>0.6779923242463303</v>
       </c>
       <c r="U23">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V23">
         <v>0.29</v>
       </c>
       <c r="W23">
-        <v>0.036778</v>
+        <v>0.037985</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y23">
-        <v>10.13706117675872</v>
+        <v>9.368814909157294</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3219,22 +3219,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.1305497609857918</v>
+        <v>0.1302037619397986</v>
       </c>
       <c r="C24">
-        <v>83.69206125450432</v>
+        <v>83.12839783651405</v>
       </c>
       <c r="D24">
-        <v>94.78046125450433</v>
+        <v>95.16899783651405</v>
       </c>
       <c r="E24">
-        <v>15.7284</v>
+        <v>16.6806</v>
       </c>
       <c r="F24">
-        <v>20.9484</v>
+        <v>21.9006</v>
       </c>
       <c r="G24">
         <v>9.859999999999999</v>
@@ -3255,28 +3255,28 @@
         <v>10.5</v>
       </c>
       <c r="M24">
-        <v>1.1207394</v>
+        <v>1.1716821</v>
       </c>
       <c r="N24">
-        <v>9.3792606</v>
+        <v>9.3283179</v>
       </c>
       <c r="O24">
-        <v>2.719985574</v>
+        <v>2.705212191</v>
       </c>
       <c r="P24">
-        <v>6.659275026</v>
+        <v>6.623105709000001</v>
       </c>
       <c r="Q24">
-        <v>10.559275026</v>
+        <v>10.523105709</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1566577704946049</v>
+        <v>0.1577496258958424</v>
       </c>
       <c r="T24">
-        <v>0.6779923242463303</v>
+        <v>0.6846699759609836</v>
       </c>
       <c r="U24">
         <v>0.0535</v>
@@ -3293,7 +3293,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>9.368814909157294</v>
+        <v>8.961475130498282</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3301,22 +3301,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1302037619397986</v>
+        <v>0.1298577628938055</v>
       </c>
       <c r="C25">
-        <v>83.12839783651405</v>
+        <v>82.56793301154075</v>
       </c>
       <c r="D25">
-        <v>95.16899783651405</v>
+        <v>95.56073301154075</v>
       </c>
       <c r="E25">
-        <v>16.6806</v>
+        <v>17.6328</v>
       </c>
       <c r="F25">
-        <v>21.9006</v>
+        <v>22.8528</v>
       </c>
       <c r="G25">
         <v>9.859999999999999</v>
@@ -3337,28 +3337,28 @@
         <v>10.5</v>
       </c>
       <c r="M25">
-        <v>1.1716821</v>
+        <v>1.2226248</v>
       </c>
       <c r="N25">
-        <v>9.3283179</v>
+        <v>9.2773752</v>
       </c>
       <c r="O25">
-        <v>2.705212191</v>
+        <v>2.690438808</v>
       </c>
       <c r="P25">
-        <v>6.623105709000001</v>
+        <v>6.586936392</v>
       </c>
       <c r="Q25">
-        <v>10.523105709</v>
+        <v>10.486936392</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1577496258958424</v>
+        <v>0.1588702143339546</v>
       </c>
       <c r="T25">
-        <v>0.6846699759609836</v>
+        <v>0.6915233553523381</v>
       </c>
       <c r="U25">
         <v>0.0535</v>
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>8.961475130498282</v>
+        <v>8.588080333394185</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3383,22 +3383,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1298577628938055</v>
+        <v>0.1295117638478123</v>
       </c>
       <c r="C26">
-        <v>82.56793301154075</v>
+        <v>82.01070644103999</v>
       </c>
       <c r="D26">
-        <v>95.56073301154075</v>
+        <v>95.95570644103998</v>
       </c>
       <c r="E26">
-        <v>17.6328</v>
+        <v>18.585</v>
       </c>
       <c r="F26">
-        <v>22.8528</v>
+        <v>23.805</v>
       </c>
       <c r="G26">
         <v>9.859999999999999</v>
@@ -3419,28 +3419,28 @@
         <v>10.5</v>
       </c>
       <c r="M26">
-        <v>1.2226248</v>
+        <v>1.2735675</v>
       </c>
       <c r="N26">
-        <v>9.2773752</v>
+        <v>9.2264325</v>
       </c>
       <c r="O26">
-        <v>2.690438808</v>
+        <v>2.675665425</v>
       </c>
       <c r="P26">
-        <v>6.586936392</v>
+        <v>6.550767075</v>
       </c>
       <c r="Q26">
-        <v>10.486936392</v>
+        <v>10.450767075</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1588702143339546</v>
+        <v>0.1600206851304164</v>
       </c>
       <c r="T26">
-        <v>0.6915233553523381</v>
+        <v>0.6985594915274622</v>
       </c>
       <c r="U26">
         <v>0.0535</v>
@@ -3457,7 +3457,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>8.588080333394185</v>
+        <v>8.244557120058419</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3465,22 +3465,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1295117638478123</v>
+        <v>0.1291657648018192</v>
       </c>
       <c r="C27">
-        <v>82.01070644103999</v>
+        <v>81.45675844490663</v>
       </c>
       <c r="D27">
-        <v>95.95570644103998</v>
+        <v>96.35395844490662</v>
       </c>
       <c r="E27">
-        <v>18.585</v>
+        <v>19.5372</v>
       </c>
       <c r="F27">
-        <v>23.805</v>
+        <v>24.7572</v>
       </c>
       <c r="G27">
         <v>9.859999999999999</v>
@@ -3501,28 +3501,28 @@
         <v>10.5</v>
       </c>
       <c r="M27">
-        <v>1.2735675</v>
+        <v>1.3245102</v>
       </c>
       <c r="N27">
-        <v>9.2264325</v>
+        <v>9.175489799999999</v>
       </c>
       <c r="O27">
-        <v>2.675665425</v>
+        <v>2.660892042</v>
       </c>
       <c r="P27">
-        <v>6.550767075</v>
+        <v>6.514597758</v>
       </c>
       <c r="Q27">
-        <v>10.450767075</v>
+        <v>10.414597758</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1600206851304164</v>
+        <v>0.1612022497321881</v>
       </c>
       <c r="T27">
-        <v>0.6985594915274622</v>
+        <v>0.7057857935451574</v>
       </c>
       <c r="U27">
         <v>0.0535</v>
@@ -3539,7 +3539,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>8.244557120058419</v>
+        <v>7.92745876928694</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3547,22 +3547,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1291657648018192</v>
+        <v>0.128819765755826</v>
       </c>
       <c r="C28">
-        <v>81.45675844490663</v>
+        <v>80.90613001519576</v>
       </c>
       <c r="D28">
-        <v>96.35395844490662</v>
+        <v>96.75553001519576</v>
       </c>
       <c r="E28">
-        <v>19.5372</v>
+        <v>20.4894</v>
       </c>
       <c r="F28">
-        <v>24.7572</v>
+        <v>25.7094</v>
       </c>
       <c r="G28">
         <v>9.859999999999999</v>
@@ -3583,28 +3583,28 @@
         <v>10.5</v>
       </c>
       <c r="M28">
-        <v>1.3245102</v>
+        <v>1.3754529</v>
       </c>
       <c r="N28">
-        <v>9.175489799999999</v>
+        <v>9.124547099999999</v>
       </c>
       <c r="O28">
-        <v>2.660892042</v>
+        <v>2.646118658999999</v>
       </c>
       <c r="P28">
-        <v>6.514597758</v>
+        <v>6.478428441</v>
       </c>
       <c r="Q28">
-        <v>10.414597758</v>
+        <v>10.378428441</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1612022497321881</v>
+        <v>0.1624161859668849</v>
       </c>
       <c r="T28">
-        <v>0.7057857935451574</v>
+        <v>0.7132100764400494</v>
       </c>
       <c r="U28">
         <v>0.0535</v>
@@ -3621,7 +3621,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>7.92745876928694</v>
+        <v>7.633849185239275</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3629,22 +3629,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.128819765755826</v>
+        <v>0.1286328067098328</v>
       </c>
       <c r="C29">
-        <v>80.90613001519576</v>
+        <v>80.17231355554311</v>
       </c>
       <c r="D29">
-        <v>96.75553001519576</v>
+        <v>96.97391355554312</v>
       </c>
       <c r="E29">
-        <v>20.4894</v>
+        <v>21.4416</v>
       </c>
       <c r="F29">
-        <v>25.7094</v>
+        <v>26.6616</v>
       </c>
       <c r="G29">
         <v>9.859999999999999</v>
@@ -3665,45 +3665,45 @@
         <v>10.5</v>
       </c>
       <c r="M29">
-        <v>1.3754529</v>
+        <v>1.44772488</v>
       </c>
       <c r="N29">
-        <v>9.124547099999999</v>
+        <v>9.052275119999999</v>
       </c>
       <c r="O29">
-        <v>2.646118658999999</v>
+        <v>2.6251597848</v>
       </c>
       <c r="P29">
-        <v>6.478428441</v>
+        <v>6.4271153352</v>
       </c>
       <c r="Q29">
-        <v>10.378428441</v>
+        <v>10.3271153352</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1624161859668849</v>
+        <v>0.1636638426525456</v>
       </c>
       <c r="T29">
-        <v>0.7132100764400494</v>
+        <v>0.7208405894153553</v>
       </c>
       <c r="U29">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V29">
         <v>0.29</v>
       </c>
       <c r="W29">
-        <v>0.037985</v>
+        <v>0.038553</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y29">
-        <v>7.633849185239275</v>
+        <v>7.25275923972516</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3711,22 +3711,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1286328067098328</v>
+        <v>0.1282924876638397</v>
       </c>
       <c r="C30">
-        <v>80.17231355554311</v>
+        <v>79.62017507244067</v>
       </c>
       <c r="D30">
-        <v>96.97391355554312</v>
+        <v>97.37397507244067</v>
       </c>
       <c r="E30">
-        <v>21.4416</v>
+        <v>22.39380000000001</v>
       </c>
       <c r="F30">
-        <v>26.6616</v>
+        <v>27.6138</v>
       </c>
       <c r="G30">
         <v>9.859999999999999</v>
@@ -3747,28 +3747,28 @@
         <v>10.5</v>
       </c>
       <c r="M30">
-        <v>1.44772488</v>
+        <v>1.49942934</v>
       </c>
       <c r="N30">
-        <v>9.052275119999999</v>
+        <v>9.000570659999999</v>
       </c>
       <c r="O30">
-        <v>2.6251597848</v>
+        <v>2.6101654914</v>
       </c>
       <c r="P30">
-        <v>6.4271153352</v>
+        <v>6.390405168599999</v>
       </c>
       <c r="Q30">
-        <v>10.3271153352</v>
+        <v>10.2904051686</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1636638426525456</v>
+        <v>0.1649466445969573</v>
       </c>
       <c r="T30">
-        <v>0.7208405894153553</v>
+        <v>0.7286860464181345</v>
       </c>
       <c r="U30">
         <v>0.0543</v>
@@ -3785,7 +3785,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>7.25275923972516</v>
+        <v>7.00266409352774</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3793,22 +3793,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1282924876638397</v>
+        <v>0.1279521686178465</v>
       </c>
       <c r="C31">
-        <v>79.62017507244067</v>
+        <v>79.07135113492011</v>
       </c>
       <c r="D31">
-        <v>97.37397507244067</v>
+        <v>97.77735113492011</v>
       </c>
       <c r="E31">
-        <v>22.3938</v>
+        <v>23.346</v>
       </c>
       <c r="F31">
-        <v>27.6138</v>
+        <v>28.566</v>
       </c>
       <c r="G31">
         <v>9.859999999999999</v>
@@ -3829,28 +3829,28 @@
         <v>10.5</v>
       </c>
       <c r="M31">
-        <v>1.49942934</v>
+        <v>1.5511338</v>
       </c>
       <c r="N31">
-        <v>9.000570660000001</v>
+        <v>8.948866199999999</v>
       </c>
       <c r="O31">
-        <v>2.6101654914</v>
+        <v>2.595171198</v>
       </c>
       <c r="P31">
-        <v>6.390405168600001</v>
+        <v>6.353695002</v>
       </c>
       <c r="Q31">
-        <v>10.2904051686</v>
+        <v>10.253695002</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1649466445969573</v>
+        <v>0.166266098025495</v>
       </c>
       <c r="T31">
-        <v>0.7286860464181345</v>
+        <v>0.7367556593352789</v>
       </c>
       <c r="U31">
         <v>0.0543</v>
@@ -3867,7 +3867,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>7.002664093527743</v>
+        <v>6.769241957076817</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1279521686178465</v>
+        <v>0.1276118495718533</v>
       </c>
       <c r="C32">
-        <v>79.07135113492011</v>
+        <v>78.52588310629241</v>
       </c>
       <c r="D32">
-        <v>97.77735113492011</v>
+        <v>98.18408310629242</v>
       </c>
       <c r="E32">
-        <v>23.346</v>
+        <v>24.2982</v>
       </c>
       <c r="F32">
-        <v>28.566</v>
+        <v>29.5182</v>
       </c>
       <c r="G32">
         <v>9.859999999999999</v>
@@ -3911,28 +3911,28 @@
         <v>10.5</v>
       </c>
       <c r="M32">
-        <v>1.5511338</v>
+        <v>1.60283826</v>
       </c>
       <c r="N32">
-        <v>8.948866199999999</v>
+        <v>8.89716174</v>
       </c>
       <c r="O32">
-        <v>2.595171198</v>
+        <v>2.5801769046</v>
       </c>
       <c r="P32">
-        <v>6.353695002</v>
+        <v>6.3169848354</v>
       </c>
       <c r="Q32">
-        <v>10.253695002</v>
+        <v>10.2169848354</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.166266098025495</v>
+        <v>0.1676237964809469</v>
       </c>
       <c r="T32">
-        <v>0.7367556593352789</v>
+        <v>0.7450591740761086</v>
       </c>
       <c r="U32">
         <v>0.0543</v>
@@ -3949,7 +3949,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>6.769241957076817</v>
+        <v>6.550879313300145</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3957,22 +3957,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1276118495718533</v>
+        <v>0.1272715305258602</v>
       </c>
       <c r="C33">
-        <v>78.52588310629241</v>
+        <v>77.983813040992</v>
       </c>
       <c r="D33">
-        <v>98.18408310629242</v>
+        <v>98.594213040992</v>
       </c>
       <c r="E33">
-        <v>24.2982</v>
+        <v>25.2504</v>
       </c>
       <c r="F33">
-        <v>29.5182</v>
+        <v>30.4704</v>
       </c>
       <c r="G33">
         <v>9.859999999999999</v>
@@ -3993,28 +3993,28 @@
         <v>10.5</v>
       </c>
       <c r="M33">
-        <v>1.60283826</v>
+        <v>1.65454272</v>
       </c>
       <c r="N33">
-        <v>8.89716174</v>
+        <v>8.84545728</v>
       </c>
       <c r="O33">
-        <v>2.5801769046</v>
+        <v>2.5651826112</v>
       </c>
       <c r="P33">
-        <v>6.3169848354</v>
+        <v>6.280274668800001</v>
       </c>
       <c r="Q33">
-        <v>10.2169848354</v>
+        <v>10.1802746688</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1676237964809469</v>
+        <v>0.1690214272439121</v>
       </c>
       <c r="T33">
-        <v>0.7450591740761086</v>
+        <v>0.7536069098387274</v>
       </c>
       <c r="U33">
         <v>0.0543</v>
@@ -4031,7 +4031,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>6.550879313300145</v>
+        <v>6.346164334759516</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4039,22 +4039,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1272715305258602</v>
+        <v>0.126931211479867</v>
       </c>
       <c r="C34">
-        <v>77.983813040992</v>
+        <v>77.445183699072</v>
       </c>
       <c r="D34">
-        <v>98.594213040992</v>
+        <v>99.00778369907201</v>
       </c>
       <c r="E34">
-        <v>25.2504</v>
+        <v>26.2026</v>
       </c>
       <c r="F34">
-        <v>30.4704</v>
+        <v>31.4226</v>
       </c>
       <c r="G34">
         <v>9.859999999999999</v>
@@ -4075,28 +4075,28 @@
         <v>10.5</v>
       </c>
       <c r="M34">
-        <v>1.65454272</v>
+        <v>1.70624718</v>
       </c>
       <c r="N34">
-        <v>8.84545728</v>
+        <v>8.79375282</v>
       </c>
       <c r="O34">
-        <v>2.5651826112</v>
+        <v>2.5501883178</v>
       </c>
       <c r="P34">
-        <v>6.280274668800001</v>
+        <v>6.2435645022</v>
       </c>
       <c r="Q34">
-        <v>10.1802746688</v>
+        <v>10.1435645022</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1690214272439121</v>
+        <v>0.1704607783281598</v>
       </c>
       <c r="T34">
-        <v>0.7536069098387274</v>
+        <v>0.7624098018927676</v>
       </c>
       <c r="U34">
         <v>0.0543</v>
@@ -4113,7 +4113,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>6.346164334759516</v>
+        <v>6.153856324615288</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4121,22 +4121,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.126931211479867</v>
+        <v>0.1268322924338739</v>
       </c>
       <c r="C35">
-        <v>77.445183699072</v>
+        <v>76.61384607646804</v>
       </c>
       <c r="D35">
-        <v>99.00778369907201</v>
+        <v>99.12864607646804</v>
       </c>
       <c r="E35">
-        <v>26.2026</v>
+        <v>27.1548</v>
       </c>
       <c r="F35">
-        <v>31.4226</v>
+        <v>32.3748</v>
       </c>
       <c r="G35">
         <v>9.859999999999999</v>
@@ -4157,45 +4157,45 @@
         <v>10.5</v>
       </c>
       <c r="M35">
-        <v>1.70624718</v>
+        <v>1.79032644</v>
       </c>
       <c r="N35">
-        <v>8.79375282</v>
+        <v>8.709673560000001</v>
       </c>
       <c r="O35">
-        <v>2.5501883178</v>
+        <v>2.5258053324</v>
       </c>
       <c r="P35">
-        <v>6.2435645022</v>
+        <v>6.183868227600001</v>
       </c>
       <c r="Q35">
-        <v>10.1435645022</v>
+        <v>10.0838682276</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1704607783281598</v>
+        <v>0.1719437461119301</v>
       </c>
       <c r="T35">
-        <v>0.7624098018927676</v>
+        <v>0.7714794482514757</v>
       </c>
       <c r="U35">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V35">
         <v>0.29</v>
       </c>
       <c r="W35">
-        <v>0.038553</v>
+        <v>0.039263</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y35">
-        <v>6.153856324615288</v>
+        <v>5.864852222145588</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4203,22 +4203,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1268322924338739</v>
+        <v>0.1264990733878807</v>
       </c>
       <c r="C36">
-        <v>76.61384607646804</v>
+        <v>76.07096369920487</v>
       </c>
       <c r="D36">
-        <v>99.12864607646804</v>
+        <v>99.53796369920488</v>
       </c>
       <c r="E36">
-        <v>27.1548</v>
+        <v>28.10700000000001</v>
       </c>
       <c r="F36">
-        <v>32.3748</v>
+        <v>33.32700000000001</v>
       </c>
       <c r="G36">
         <v>9.859999999999999</v>
@@ -4239,28 +4239,28 @@
         <v>10.5</v>
       </c>
       <c r="M36">
-        <v>1.79032644</v>
+        <v>1.8429831</v>
       </c>
       <c r="N36">
-        <v>8.709673560000001</v>
+        <v>8.6570169</v>
       </c>
       <c r="O36">
-        <v>2.5258053324</v>
+        <v>2.510534901</v>
       </c>
       <c r="P36">
-        <v>6.183868227600001</v>
+        <v>6.146481999000001</v>
       </c>
       <c r="Q36">
-        <v>10.0838682276</v>
+        <v>10.046481999</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1719437461119301</v>
+        <v>0.1734723436736627</v>
       </c>
       <c r="T36">
-        <v>0.7714794482514757</v>
+        <v>0.7808281606519903</v>
       </c>
       <c r="U36">
         <v>0.0553</v>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>5.864852222145588</v>
+        <v>5.69728501579857</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4285,22 +4285,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1264990733878807</v>
+        <v>0.1261658543418875</v>
       </c>
       <c r="C37">
-        <v>76.07096369920487</v>
+        <v>75.53147560994812</v>
       </c>
       <c r="D37">
-        <v>99.53796369920488</v>
+        <v>99.95067560994812</v>
       </c>
       <c r="E37">
-        <v>28.10700000000001</v>
+        <v>29.0592</v>
       </c>
       <c r="F37">
-        <v>33.32700000000001</v>
+        <v>34.2792</v>
       </c>
       <c r="G37">
         <v>9.859999999999999</v>
@@ -4321,28 +4321,28 @@
         <v>10.5</v>
       </c>
       <c r="M37">
-        <v>1.8429831</v>
+        <v>1.89563976</v>
       </c>
       <c r="N37">
-        <v>8.6570169</v>
+        <v>8.60436024</v>
       </c>
       <c r="O37">
-        <v>2.510534901</v>
+        <v>2.4952644696</v>
       </c>
       <c r="P37">
-        <v>6.146481999000001</v>
+        <v>6.1090957704</v>
       </c>
       <c r="Q37">
-        <v>10.046481999</v>
+        <v>10.0090957704</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1734723436736627</v>
+        <v>0.1750487099091993</v>
       </c>
       <c r="T37">
-        <v>0.7808281606519903</v>
+        <v>0.790469020315021</v>
       </c>
       <c r="U37">
         <v>0.0553</v>
@@ -4359,7 +4359,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>5.69728501579857</v>
+        <v>5.539027098693055</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4367,22 +4367,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1261658543418876</v>
+        <v>0.1258326352958944</v>
       </c>
       <c r="C38">
-        <v>75.53147560994807</v>
+        <v>74.99542420545521</v>
       </c>
       <c r="D38">
-        <v>99.95067560994808</v>
+        <v>100.3668242054552</v>
       </c>
       <c r="E38">
-        <v>29.0592</v>
+        <v>30.0114</v>
       </c>
       <c r="F38">
-        <v>34.2792</v>
+        <v>35.2314</v>
       </c>
       <c r="G38">
         <v>9.859999999999999</v>
@@ -4403,28 +4403,28 @@
         <v>10.5</v>
       </c>
       <c r="M38">
-        <v>1.89563976</v>
+        <v>1.94829642</v>
       </c>
       <c r="N38">
-        <v>8.60436024</v>
+        <v>8.55170358</v>
       </c>
       <c r="O38">
-        <v>2.4952644696</v>
+        <v>2.4799940382</v>
       </c>
       <c r="P38">
-        <v>6.1090957704</v>
+        <v>6.071709541800001</v>
       </c>
       <c r="Q38">
-        <v>10.0090957704</v>
+        <v>9.971709541800001</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1750487099091993</v>
+        <v>0.1766751195172927</v>
       </c>
       <c r="T38">
-        <v>0.790469020315021</v>
+        <v>0.8004159390149732</v>
       </c>
       <c r="U38">
         <v>0.0553</v>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>5.539027098693055</v>
+        <v>5.389323663593243</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4449,22 +4449,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1258326352958944</v>
+        <v>0.1254994162499012</v>
       </c>
       <c r="C39">
-        <v>74.99542420545521</v>
+        <v>74.46285259151814</v>
       </c>
       <c r="D39">
-        <v>100.3668242054552</v>
+        <v>100.7864525915181</v>
       </c>
       <c r="E39">
-        <v>30.0114</v>
+        <v>30.9636</v>
       </c>
       <c r="F39">
-        <v>35.2314</v>
+        <v>36.1836</v>
       </c>
       <c r="G39">
         <v>9.859999999999999</v>
@@ -4485,28 +4485,28 @@
         <v>10.5</v>
       </c>
       <c r="M39">
-        <v>1.94829642</v>
+        <v>2.00095308</v>
       </c>
       <c r="N39">
-        <v>8.55170358</v>
+        <v>8.49904692</v>
       </c>
       <c r="O39">
-        <v>2.4799940382</v>
+        <v>2.4647236068</v>
       </c>
       <c r="P39">
-        <v>6.071709541800001</v>
+        <v>6.0343233132</v>
       </c>
       <c r="Q39">
-        <v>9.971709541800001</v>
+        <v>9.9343233132</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1766751195172927</v>
+        <v>0.1783539939514536</v>
       </c>
       <c r="T39">
-        <v>0.8004159390149732</v>
+        <v>0.8106837260600851</v>
       </c>
       <c r="U39">
         <v>0.0553</v>
@@ -4523,7 +4523,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>5.389323663593243</v>
+        <v>5.247499356656578</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4531,22 +4531,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1254994162499012</v>
+        <v>0.1251661972039081</v>
       </c>
       <c r="C40">
-        <v>74.46285259151814</v>
+        <v>73.93380459784768</v>
       </c>
       <c r="D40">
-        <v>100.7864525915181</v>
+        <v>101.2096045978477</v>
       </c>
       <c r="E40">
-        <v>30.9636</v>
+        <v>31.9158</v>
       </c>
       <c r="F40">
-        <v>36.1836</v>
+        <v>37.1358</v>
       </c>
       <c r="G40">
         <v>9.859999999999999</v>
@@ -4567,28 +4567,28 @@
         <v>10.5</v>
       </c>
       <c r="M40">
-        <v>2.00095308</v>
+        <v>2.05360974</v>
       </c>
       <c r="N40">
-        <v>8.49904692</v>
+        <v>8.446390259999999</v>
       </c>
       <c r="O40">
-        <v>2.4647236068</v>
+        <v>2.4494531754</v>
       </c>
       <c r="P40">
-        <v>6.0343233132</v>
+        <v>5.9969370846</v>
       </c>
       <c r="Q40">
-        <v>9.9343233132</v>
+        <v>9.896937084600001</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1783539939514536</v>
+        <v>0.1800879134490296</v>
       </c>
       <c r="T40">
-        <v>0.8106837260600851</v>
+        <v>0.8212881618607746</v>
       </c>
       <c r="U40">
         <v>0.0553</v>
@@ -4605,7 +4605,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>5.247499356656578</v>
+        <v>5.112948091101281</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4613,22 +4613,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1251661972039081</v>
+        <v>0.1248329781579149</v>
       </c>
       <c r="C41">
-        <v>73.93380459784768</v>
+        <v>73.40832479333434</v>
       </c>
       <c r="D41">
-        <v>101.2096045978477</v>
+        <v>101.6363247933344</v>
       </c>
       <c r="E41">
-        <v>31.9158</v>
+        <v>32.868</v>
       </c>
       <c r="F41">
-        <v>37.1358</v>
+        <v>38.088</v>
       </c>
       <c r="G41">
         <v>9.859999999999999</v>
@@ -4649,28 +4649,28 @@
         <v>10.5</v>
       </c>
       <c r="M41">
-        <v>2.05360974</v>
+        <v>2.1062664</v>
       </c>
       <c r="N41">
-        <v>8.446390259999999</v>
+        <v>8.393733600000001</v>
       </c>
       <c r="O41">
-        <v>2.4494531754</v>
+        <v>2.434182744</v>
       </c>
       <c r="P41">
-        <v>5.9969370846</v>
+        <v>5.959550856000001</v>
       </c>
       <c r="Q41">
-        <v>9.896937084600001</v>
+        <v>9.859550856000002</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1800879134490296</v>
+        <v>0.1818796302631915</v>
       </c>
       <c r="T41">
-        <v>0.8212881618607746</v>
+        <v>0.8322460788548204</v>
       </c>
       <c r="U41">
         <v>0.0553</v>
@@ -4687,7 +4687,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>5.112948091101281</v>
+        <v>4.985124388823751</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4695,22 +4695,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1248329781579149</v>
+        <v>0.1244997591119218</v>
       </c>
       <c r="C42">
-        <v>73.40832479333434</v>
+        <v>72.88645850169706</v>
       </c>
       <c r="D42">
-        <v>101.6363247933344</v>
+        <v>102.0666585016971</v>
       </c>
       <c r="E42">
-        <v>32.868</v>
+        <v>33.82020000000001</v>
       </c>
       <c r="F42">
-        <v>38.088</v>
+        <v>39.04020000000001</v>
       </c>
       <c r="G42">
         <v>9.859999999999999</v>
@@ -4731,28 +4731,28 @@
         <v>10.5</v>
       </c>
       <c r="M42">
-        <v>2.1062664</v>
+        <v>2.15892306</v>
       </c>
       <c r="N42">
-        <v>8.393733600000001</v>
+        <v>8.341076940000001</v>
       </c>
       <c r="O42">
-        <v>2.434182744</v>
+        <v>2.4189123126</v>
       </c>
       <c r="P42">
-        <v>5.959550856000001</v>
+        <v>5.922164627400001</v>
       </c>
       <c r="Q42">
-        <v>9.859550856000002</v>
+        <v>9.822164627400001</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1818796302631915</v>
+        <v>0.1837320832405454</v>
       </c>
       <c r="T42">
-        <v>0.8322460788548204</v>
+        <v>0.8435754506622235</v>
       </c>
       <c r="U42">
         <v>0.0553</v>
@@ -4769,7 +4769,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>4.985124388823751</v>
+        <v>4.863535989096341</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4777,22 +4777,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1244997591119218</v>
+        <v>0.1241665400659286</v>
       </c>
       <c r="C43">
-        <v>72.88645850169706</v>
+        <v>72.36825181753103</v>
       </c>
       <c r="D43">
-        <v>102.0666585016971</v>
+        <v>102.500651817531</v>
       </c>
       <c r="E43">
-        <v>33.82020000000001</v>
+        <v>34.7724</v>
       </c>
       <c r="F43">
-        <v>39.04020000000001</v>
+        <v>39.9924</v>
       </c>
       <c r="G43">
         <v>9.859999999999999</v>
@@ -4813,28 +4813,28 @@
         <v>10.5</v>
       </c>
       <c r="M43">
-        <v>2.15892306</v>
+        <v>2.21157972</v>
       </c>
       <c r="N43">
-        <v>8.341076940000001</v>
+        <v>8.28842028</v>
       </c>
       <c r="O43">
-        <v>2.4189123126</v>
+        <v>2.4036418812</v>
       </c>
       <c r="P43">
-        <v>5.922164627400001</v>
+        <v>5.8847783988</v>
       </c>
       <c r="Q43">
-        <v>9.822164627400001</v>
+        <v>9.7847783988</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1837320832405454</v>
+        <v>0.1856484139067734</v>
       </c>
       <c r="T43">
-        <v>0.8435754506622235</v>
+        <v>0.8552954904629855</v>
       </c>
       <c r="U43">
         <v>0.0553</v>
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>4.863535989096341</v>
+        <v>4.747737513165475</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4859,22 +4859,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1241665400659286</v>
+        <v>0.1238333210199355</v>
       </c>
       <c r="C44">
-        <v>72.36825181753102</v>
+        <v>71.85375162276662</v>
       </c>
       <c r="D44">
-        <v>102.500651817531</v>
+        <v>102.9383516227666</v>
       </c>
       <c r="E44">
-        <v>34.7724</v>
+        <v>35.7246</v>
       </c>
       <c r="F44">
-        <v>39.9924</v>
+        <v>40.9446</v>
       </c>
       <c r="G44">
         <v>9.859999999999999</v>
@@ -4895,28 +4895,28 @@
         <v>10.5</v>
       </c>
       <c r="M44">
-        <v>2.21157972</v>
+        <v>2.26423638</v>
       </c>
       <c r="N44">
-        <v>8.28842028</v>
+        <v>8.23576362</v>
       </c>
       <c r="O44">
-        <v>2.4036418812</v>
+        <v>2.3883714498</v>
       </c>
       <c r="P44">
-        <v>5.8847783988</v>
+        <v>5.847392170200001</v>
       </c>
       <c r="Q44">
-        <v>9.7847783988</v>
+        <v>9.747392170200001</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1856484139067734</v>
+        <v>0.1876319842455008</v>
       </c>
       <c r="T44">
-        <v>0.8552954904629855</v>
+        <v>0.8674267597304408</v>
       </c>
       <c r="U44">
         <v>0.0553</v>
@@ -4933,7 +4933,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>4.747737513165476</v>
+        <v>4.637325012859302</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1238333210199355</v>
+        <v>0.1235001019739423</v>
       </c>
       <c r="C45">
-        <v>71.85375162276662</v>
+        <v>71.34300560355227</v>
       </c>
       <c r="D45">
-        <v>102.9383516227666</v>
+        <v>103.3798056035523</v>
       </c>
       <c r="E45">
-        <v>35.7246</v>
+        <v>36.6768</v>
       </c>
       <c r="F45">
-        <v>40.9446</v>
+        <v>41.8968</v>
       </c>
       <c r="G45">
         <v>9.859999999999999</v>
@@ -4977,28 +4977,28 @@
         <v>10.5</v>
       </c>
       <c r="M45">
-        <v>2.26423638</v>
+        <v>2.31689304</v>
       </c>
       <c r="N45">
-        <v>8.23576362</v>
+        <v>8.18310696</v>
       </c>
       <c r="O45">
-        <v>2.3883714498</v>
+        <v>2.3731010184</v>
       </c>
       <c r="P45">
-        <v>5.847392170200001</v>
+        <v>5.8100059416</v>
       </c>
       <c r="Q45">
-        <v>9.747392170200001</v>
+        <v>9.7100059416</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1876319842455008</v>
+        <v>0.1896863963820398</v>
       </c>
       <c r="T45">
-        <v>0.8674267597304408</v>
+        <v>0.879991288614591</v>
       </c>
       <c r="U45">
         <v>0.0553</v>
@@ -5015,7 +5015,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>4.637325012859302</v>
+        <v>4.531931262567046</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5023,22 +5023,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1235001019739423</v>
+        <v>0.1239656329279491</v>
       </c>
       <c r="C46">
-        <v>71.34300560355227</v>
+        <v>69.77510663554129</v>
       </c>
       <c r="D46">
-        <v>103.3798056035523</v>
+        <v>102.7641066355413</v>
       </c>
       <c r="E46">
-        <v>36.6768</v>
+        <v>37.629</v>
       </c>
       <c r="F46">
-        <v>41.8968</v>
+        <v>42.849</v>
       </c>
       <c r="G46">
         <v>9.859999999999999</v>
@@ -5059,45 +5059,45 @@
         <v>10.5</v>
       </c>
       <c r="M46">
-        <v>2.31689304</v>
+        <v>2.4766722</v>
       </c>
       <c r="N46">
-        <v>8.18310696</v>
+        <v>8.023327800000001</v>
       </c>
       <c r="O46">
-        <v>2.3731010184</v>
+        <v>2.326765062</v>
       </c>
       <c r="P46">
-        <v>5.8100059416</v>
+        <v>5.696562738000001</v>
       </c>
       <c r="Q46">
-        <v>9.7100059416</v>
+        <v>9.596562738000001</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1896863963820398</v>
+        <v>0.1918155144144529</v>
       </c>
       <c r="T46">
-        <v>0.879991288614591</v>
+        <v>0.8930127094581648</v>
       </c>
       <c r="U46">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V46">
         <v>0.29</v>
       </c>
       <c r="W46">
-        <v>0.039263</v>
+        <v>0.041038</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y46">
-        <v>4.531931262567046</v>
+        <v>4.239559841629426</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5105,22 +5105,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1239656329279491</v>
+        <v>0.123650163881956</v>
       </c>
       <c r="C47">
-        <v>69.77510663554129</v>
+        <v>69.23933343628391</v>
       </c>
       <c r="D47">
-        <v>102.7641066355413</v>
+        <v>103.1805334362839</v>
       </c>
       <c r="E47">
-        <v>37.629</v>
+        <v>38.5812</v>
       </c>
       <c r="F47">
-        <v>42.849</v>
+        <v>43.8012</v>
       </c>
       <c r="G47">
         <v>9.859999999999999</v>
@@ -5141,28 +5141,28 @@
         <v>10.5</v>
       </c>
       <c r="M47">
-        <v>2.4766722</v>
+        <v>2.53170936</v>
       </c>
       <c r="N47">
-        <v>8.023327800000001</v>
+        <v>7.968290639999999</v>
       </c>
       <c r="O47">
-        <v>2.326765062</v>
+        <v>2.3108042856</v>
       </c>
       <c r="P47">
-        <v>5.696562738000001</v>
+        <v>5.6574863544</v>
       </c>
       <c r="Q47">
-        <v>9.596562738000001</v>
+        <v>9.5574863544</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1918155144144529</v>
+        <v>0.1940234886702888</v>
       </c>
       <c r="T47">
-        <v>0.8930127094581648</v>
+        <v>0.9065164051477971</v>
       </c>
       <c r="U47">
         <v>0.0578</v>
@@ -5179,7 +5179,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>4.239559841629426</v>
+        <v>4.147395497246176</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5187,22 +5187,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.123650163881956</v>
+        <v>0.1233346948359628</v>
       </c>
       <c r="C48">
-        <v>69.23933343628391</v>
+        <v>68.70694890750073</v>
       </c>
       <c r="D48">
-        <v>103.1805334362839</v>
+        <v>103.6003489075007</v>
       </c>
       <c r="E48">
-        <v>38.5812</v>
+        <v>39.5334</v>
       </c>
       <c r="F48">
-        <v>43.8012</v>
+        <v>44.7534</v>
       </c>
       <c r="G48">
         <v>9.859999999999999</v>
@@ -5223,28 +5223,28 @@
         <v>10.5</v>
       </c>
       <c r="M48">
-        <v>2.53170936</v>
+        <v>2.58674652</v>
       </c>
       <c r="N48">
-        <v>7.968290639999999</v>
+        <v>7.91325348</v>
       </c>
       <c r="O48">
-        <v>2.3108042856</v>
+        <v>2.2948435092</v>
       </c>
       <c r="P48">
-        <v>5.6574863544</v>
+        <v>5.6184099708</v>
       </c>
       <c r="Q48">
-        <v>9.5574863544</v>
+        <v>9.518409970800001</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1940234886702888</v>
+        <v>0.1963147827093638</v>
       </c>
       <c r="T48">
-        <v>0.9065164051477971</v>
+        <v>0.9205296742596794</v>
       </c>
       <c r="U48">
         <v>0.0578</v>
@@ -5261,7 +5261,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>4.147395497246176</v>
+        <v>4.05915303985796</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5269,22 +5269,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1233346948359628</v>
+        <v>0.1242120257899697</v>
       </c>
       <c r="C49">
-        <v>68.70694890750073</v>
+        <v>66.59559261703683</v>
       </c>
       <c r="D49">
-        <v>103.6003489075007</v>
+        <v>102.4411926170368</v>
       </c>
       <c r="E49">
-        <v>39.5334</v>
+        <v>40.48560000000001</v>
       </c>
       <c r="F49">
-        <v>44.7534</v>
+        <v>45.7056</v>
       </c>
       <c r="G49">
         <v>9.859999999999999</v>
@@ -5305,45 +5305,45 @@
         <v>10.5</v>
       </c>
       <c r="M49">
-        <v>2.58674652</v>
+        <v>2.80175328</v>
       </c>
       <c r="N49">
-        <v>7.91325348</v>
+        <v>7.69824672</v>
       </c>
       <c r="O49">
-        <v>2.2948435092</v>
+        <v>2.2324915488</v>
       </c>
       <c r="P49">
-        <v>5.6184099708</v>
+        <v>5.4657551712</v>
       </c>
       <c r="Q49">
-        <v>9.518409970800001</v>
+        <v>9.3657551712</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1963147827093638</v>
+        <v>0.1986942034422493</v>
       </c>
       <c r="T49">
-        <v>0.9205296742596794</v>
+        <v>0.9350819152604803</v>
       </c>
       <c r="U49">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V49">
         <v>0.29</v>
       </c>
       <c r="W49">
-        <v>0.041038</v>
+        <v>0.043523</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y49">
-        <v>4.05915303985796</v>
+        <v>3.747653326562716</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5351,22 +5351,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1242120257899697</v>
+        <v>0.1239214067439765</v>
       </c>
       <c r="C50">
-        <v>66.59559261703683</v>
+        <v>66.02448357417146</v>
       </c>
       <c r="D50">
-        <v>102.4411926170368</v>
+        <v>102.8222835741715</v>
       </c>
       <c r="E50">
-        <v>40.4856</v>
+        <v>41.4378</v>
       </c>
       <c r="F50">
-        <v>45.7056</v>
+        <v>46.6578</v>
       </c>
       <c r="G50">
         <v>9.859999999999999</v>
@@ -5387,28 +5387,28 @@
         <v>10.5</v>
       </c>
       <c r="M50">
-        <v>2.80175328</v>
+        <v>2.86012314</v>
       </c>
       <c r="N50">
-        <v>7.69824672</v>
+        <v>7.639876859999999</v>
       </c>
       <c r="O50">
-        <v>2.2324915488</v>
+        <v>2.2155642894</v>
       </c>
       <c r="P50">
-        <v>5.4657551712</v>
+        <v>5.4243125706</v>
       </c>
       <c r="Q50">
-        <v>9.3657551712</v>
+        <v>9.3243125706</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1986942034422493</v>
+        <v>0.2011669347921108</v>
       </c>
       <c r="T50">
-        <v>0.9350819152604803</v>
+        <v>0.9502048323789597</v>
       </c>
       <c r="U50">
         <v>0.0613</v>
@@ -5425,7 +5425,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>3.747653326562716</v>
+        <v>3.671170605612456</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5433,22 +5433,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1239214067439765</v>
+        <v>0.1236307876979833</v>
       </c>
       <c r="C51">
-        <v>66.02448357417146</v>
+        <v>65.45622050765235</v>
       </c>
       <c r="D51">
-        <v>102.8222835741715</v>
+        <v>103.2062205076523</v>
       </c>
       <c r="E51">
-        <v>41.4378</v>
+        <v>42.39</v>
       </c>
       <c r="F51">
-        <v>46.6578</v>
+        <v>47.61</v>
       </c>
       <c r="G51">
         <v>9.859999999999999</v>
@@ -5469,28 +5469,28 @@
         <v>10.5</v>
       </c>
       <c r="M51">
-        <v>2.86012314</v>
+        <v>2.918493</v>
       </c>
       <c r="N51">
-        <v>7.639876859999999</v>
+        <v>7.581507</v>
       </c>
       <c r="O51">
-        <v>2.2155642894</v>
+        <v>2.19863703</v>
       </c>
       <c r="P51">
-        <v>5.4243125706</v>
+        <v>5.38286997</v>
       </c>
       <c r="Q51">
-        <v>9.3243125706</v>
+        <v>9.28286997</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.2011669347921108</v>
+        <v>0.2037385753959667</v>
       </c>
       <c r="T51">
-        <v>0.9502048323789597</v>
+        <v>0.9659326661821783</v>
       </c>
       <c r="U51">
         <v>0.0613</v>
@@ -5507,7 +5507,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>3.671170605612456</v>
+        <v>3.597747193500207</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5515,22 +5515,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1236307876979833</v>
+        <v>0.1233401686519902</v>
       </c>
       <c r="C52">
-        <v>65.45622050765235</v>
+        <v>64.89083541747164</v>
       </c>
       <c r="D52">
-        <v>103.2062205076523</v>
+        <v>103.5930354174716</v>
       </c>
       <c r="E52">
-        <v>42.39</v>
+        <v>43.3422</v>
       </c>
       <c r="F52">
-        <v>47.61</v>
+        <v>48.5622</v>
       </c>
       <c r="G52">
         <v>9.859999999999999</v>
@@ -5551,28 +5551,28 @@
         <v>10.5</v>
       </c>
       <c r="M52">
-        <v>2.918493</v>
+        <v>2.97686286</v>
       </c>
       <c r="N52">
-        <v>7.581507</v>
+        <v>7.52313714</v>
       </c>
       <c r="O52">
-        <v>2.19863703</v>
+        <v>2.1817097706</v>
       </c>
       <c r="P52">
-        <v>5.38286997</v>
+        <v>5.3414273694</v>
       </c>
       <c r="Q52">
-        <v>9.28286997</v>
+        <v>9.2414273694</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.2037385753959667</v>
+        <v>0.2064151809224289</v>
       </c>
       <c r="T52">
-        <v>0.9659326661821783</v>
+        <v>0.9823024523855283</v>
       </c>
       <c r="U52">
         <v>0.0613</v>
@@ -5589,7 +5589,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>3.597747193500207</v>
+        <v>3.527203130882556</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5597,22 +5597,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1233401686519902</v>
+        <v>0.124083309605997</v>
       </c>
       <c r="C53">
-        <v>64.89083541747164</v>
+        <v>62.95523004592989</v>
       </c>
       <c r="D53">
-        <v>103.5930354174716</v>
+        <v>102.6096300459299</v>
       </c>
       <c r="E53">
-        <v>43.3422</v>
+        <v>44.2944</v>
       </c>
       <c r="F53">
-        <v>48.5622</v>
+        <v>49.5144</v>
       </c>
       <c r="G53">
         <v>9.859999999999999</v>
@@ -5633,45 +5633,45 @@
         <v>10.5</v>
       </c>
       <c r="M53">
-        <v>2.97686286</v>
+        <v>3.17387304</v>
       </c>
       <c r="N53">
-        <v>7.52313714</v>
+        <v>7.32612696</v>
       </c>
       <c r="O53">
-        <v>2.1817097706</v>
+        <v>2.1245768184</v>
       </c>
       <c r="P53">
-        <v>5.3414273694</v>
+        <v>5.2015501416</v>
       </c>
       <c r="Q53">
-        <v>9.2414273694</v>
+        <v>9.101550141600001</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.2064151809224289</v>
+        <v>0.2092033116791604</v>
       </c>
       <c r="T53">
-        <v>0.9823024523855283</v>
+        <v>0.9993543130140179</v>
       </c>
       <c r="U53">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V53">
         <v>0.29</v>
       </c>
       <c r="W53">
-        <v>0.043523</v>
+        <v>0.045511</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y53">
-        <v>3.527203130882556</v>
+        <v>3.308260874858435</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5679,22 +5679,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.124083309605997</v>
+        <v>0.1238125705600039</v>
       </c>
       <c r="C54">
-        <v>62.95523004592989</v>
+        <v>62.35913205806621</v>
       </c>
       <c r="D54">
-        <v>102.6096300459299</v>
+        <v>102.9657320580662</v>
       </c>
       <c r="E54">
-        <v>44.2944</v>
+        <v>45.2466</v>
       </c>
       <c r="F54">
-        <v>49.5144</v>
+        <v>50.4666</v>
       </c>
       <c r="G54">
         <v>9.859999999999999</v>
@@ -5715,28 +5715,28 @@
         <v>10.5</v>
       </c>
       <c r="M54">
-        <v>3.17387304</v>
+        <v>3.23490906</v>
       </c>
       <c r="N54">
-        <v>7.32612696</v>
+        <v>7.26509094</v>
       </c>
       <c r="O54">
-        <v>2.1245768184</v>
+        <v>2.1068763726</v>
       </c>
       <c r="P54">
-        <v>5.2015501416</v>
+        <v>5.1582145674</v>
       </c>
       <c r="Q54">
-        <v>9.101550141600001</v>
+        <v>9.0582145674</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.2092033116791604</v>
+        <v>0.2121100862978805</v>
       </c>
       <c r="T54">
-        <v>0.9993543130140179</v>
+        <v>1.017131784733081</v>
       </c>
       <c r="U54">
         <v>0.0641</v>
@@ -5753,7 +5753,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>3.308260874858435</v>
+        <v>3.245840858351672</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5761,22 +5761,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1238125705600039</v>
+        <v>0.1235418315140107</v>
       </c>
       <c r="C55">
-        <v>62.35913205806621</v>
+        <v>61.76551434927924</v>
       </c>
       <c r="D55">
-        <v>102.9657320580662</v>
+        <v>103.3243143492792</v>
       </c>
       <c r="E55">
-        <v>45.2466</v>
+        <v>46.19880000000001</v>
       </c>
       <c r="F55">
-        <v>50.4666</v>
+        <v>51.4188</v>
       </c>
       <c r="G55">
         <v>9.859999999999999</v>
@@ -5797,28 +5797,28 @@
         <v>10.5</v>
       </c>
       <c r="M55">
-        <v>3.23490906</v>
+        <v>3.295945080000001</v>
       </c>
       <c r="N55">
-        <v>7.26509094</v>
+        <v>7.204054919999999</v>
       </c>
       <c r="O55">
-        <v>2.1068763726</v>
+        <v>2.089175926799999</v>
       </c>
       <c r="P55">
-        <v>5.1582145674</v>
+        <v>5.1148789932</v>
       </c>
       <c r="Q55">
-        <v>9.0582145674</v>
+        <v>9.0148789932</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.2121100862978805</v>
+        <v>0.2151432424217623</v>
       </c>
       <c r="T55">
-        <v>1.017131784733081</v>
+        <v>1.035682190005148</v>
       </c>
       <c r="U55">
         <v>0.0641</v>
@@ -5835,7 +5835,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>3.245840858351672</v>
+        <v>3.185732694308122</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5843,22 +5843,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1235418315140107</v>
+        <v>0.1232710924680175</v>
       </c>
       <c r="C56">
-        <v>61.76551434927924</v>
+        <v>61.17440292314141</v>
       </c>
       <c r="D56">
-        <v>103.3243143492792</v>
+        <v>103.6854029231414</v>
       </c>
       <c r="E56">
-        <v>46.19880000000001</v>
+        <v>47.151</v>
       </c>
       <c r="F56">
-        <v>51.4188</v>
+        <v>52.371</v>
       </c>
       <c r="G56">
         <v>9.859999999999999</v>
@@ -5879,28 +5879,28 @@
         <v>10.5</v>
       </c>
       <c r="M56">
-        <v>3.295945080000001</v>
+        <v>3.3569811</v>
       </c>
       <c r="N56">
-        <v>7.204054919999999</v>
+        <v>7.1430189</v>
       </c>
       <c r="O56">
-        <v>2.089175926799999</v>
+        <v>2.071475481</v>
       </c>
       <c r="P56">
-        <v>5.1148789932</v>
+        <v>5.071543418999999</v>
       </c>
       <c r="Q56">
-        <v>9.0148789932</v>
+        <v>8.971543419</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.2151432424217623</v>
+        <v>0.2183112054844834</v>
       </c>
       <c r="T56">
-        <v>1.035682190005148</v>
+        <v>1.05505705773375</v>
       </c>
       <c r="U56">
         <v>0.0641</v>
@@ -5917,7 +5917,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>3.185732694308122</v>
+        <v>3.127810281684338</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5925,22 +5925,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1232710924680175</v>
+        <v>0.1230003534220244</v>
       </c>
       <c r="C57">
-        <v>61.17440292314141</v>
+        <v>60.58582414799992</v>
       </c>
       <c r="D57">
-        <v>103.6854029231414</v>
+        <v>104.0490241479999</v>
       </c>
       <c r="E57">
-        <v>47.151</v>
+        <v>48.10320000000001</v>
       </c>
       <c r="F57">
-        <v>52.371</v>
+        <v>53.32320000000001</v>
       </c>
       <c r="G57">
         <v>9.859999999999999</v>
@@ -5961,28 +5961,28 @@
         <v>10.5</v>
       </c>
       <c r="M57">
-        <v>3.3569811</v>
+        <v>3.41801712</v>
       </c>
       <c r="N57">
-        <v>7.1430189</v>
+        <v>7.08198288</v>
       </c>
       <c r="O57">
-        <v>2.071475481</v>
+        <v>2.0537750352</v>
       </c>
       <c r="P57">
-        <v>5.071543418999999</v>
+        <v>5.028207844800001</v>
       </c>
       <c r="Q57">
-        <v>8.971543419</v>
+        <v>8.928207844800001</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.2183112054844834</v>
+        <v>0.2216231668682372</v>
       </c>
       <c r="T57">
-        <v>1.05505705773375</v>
+        <v>1.075312601268199</v>
       </c>
       <c r="U57">
         <v>0.0641</v>
@@ -5999,7 +5999,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>3.127810281684338</v>
+        <v>3.071956526654261</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1230003534220244</v>
+        <v>0.1227296143760312</v>
       </c>
       <c r="C58">
-        <v>60.58582414799992</v>
+        <v>59.99980476339536</v>
       </c>
       <c r="D58">
-        <v>104.0490241479999</v>
+        <v>104.4152047633954</v>
       </c>
       <c r="E58">
-        <v>48.10320000000001</v>
+        <v>49.05540000000001</v>
       </c>
       <c r="F58">
-        <v>53.32320000000001</v>
+        <v>54.2754</v>
       </c>
       <c r="G58">
         <v>9.859999999999999</v>
@@ -6043,28 +6043,28 @@
         <v>10.5</v>
       </c>
       <c r="M58">
-        <v>3.41801712</v>
+        <v>3.47905314</v>
       </c>
       <c r="N58">
-        <v>7.08198288</v>
+        <v>7.02094686</v>
       </c>
       <c r="O58">
-        <v>2.0537750352</v>
+        <v>2.0360745894</v>
       </c>
       <c r="P58">
-        <v>5.028207844800001</v>
+        <v>4.9848722706</v>
       </c>
       <c r="Q58">
-        <v>8.928207844800001</v>
+        <v>8.884872270600001</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.2216231668682372</v>
+        <v>0.2250891729675145</v>
       </c>
       <c r="T58">
-        <v>1.075312601268199</v>
+        <v>1.096510263106575</v>
       </c>
       <c r="U58">
         <v>0.0641</v>
@@ -6081,7 +6081,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>3.071956526654261</v>
+        <v>3.018062552502431</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6089,22 +6089,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1227296143760312</v>
+        <v>0.125670915330038</v>
       </c>
       <c r="C59">
-        <v>59.99980476339536</v>
+        <v>55.20244360411297</v>
       </c>
       <c r="D59">
-        <v>104.4152047633954</v>
+        <v>100.570043604113</v>
       </c>
       <c r="E59">
-        <v>49.05540000000001</v>
+        <v>50.00760000000001</v>
       </c>
       <c r="F59">
-        <v>54.2754</v>
+        <v>55.22760000000001</v>
       </c>
       <c r="G59">
         <v>9.859999999999999</v>
@@ -6125,45 +6125,45 @@
         <v>10.5</v>
       </c>
       <c r="M59">
-        <v>3.47905314</v>
+        <v>3.970864440000001</v>
       </c>
       <c r="N59">
-        <v>7.02094686</v>
+        <v>6.529135559999999</v>
       </c>
       <c r="O59">
-        <v>2.0360745894</v>
+        <v>1.893449312399999</v>
       </c>
       <c r="P59">
-        <v>4.9848722706</v>
+        <v>4.635686247599999</v>
       </c>
       <c r="Q59">
-        <v>8.884872270600001</v>
+        <v>8.535686247599999</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.2250891729675145</v>
+        <v>0.2287202269762811</v>
       </c>
       <c r="T59">
-        <v>1.096510263106575</v>
+        <v>1.118717337413445</v>
       </c>
       <c r="U59">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V59">
         <v>0.29</v>
       </c>
       <c r="W59">
-        <v>0.045511</v>
+        <v>0.051049</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y59">
-        <v>3.018062552502431</v>
+        <v>2.644260502632519</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6171,22 +6171,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.125670915330038</v>
+        <v>0.1254555562840449</v>
       </c>
       <c r="C60">
-        <v>55.20244360411299</v>
+        <v>54.52214765772148</v>
       </c>
       <c r="D60">
-        <v>100.570043604113</v>
+        <v>100.8419476577215</v>
       </c>
       <c r="E60">
-        <v>50.0076</v>
+        <v>50.95979999999999</v>
       </c>
       <c r="F60">
-        <v>55.2276</v>
+        <v>56.17979999999999</v>
       </c>
       <c r="G60">
         <v>9.859999999999999</v>
@@ -6207,28 +6207,28 @@
         <v>10.5</v>
       </c>
       <c r="M60">
-        <v>3.97086444</v>
+        <v>4.03932762</v>
       </c>
       <c r="N60">
-        <v>6.52913556</v>
+        <v>6.46067238</v>
       </c>
       <c r="O60">
-        <v>1.8934493124</v>
+        <v>1.8735949902</v>
       </c>
       <c r="P60">
-        <v>4.635686247600001</v>
+        <v>4.5870773898</v>
       </c>
       <c r="Q60">
-        <v>8.535686247600001</v>
+        <v>8.4870773898</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.228720226976281</v>
+        <v>0.2325284055708412</v>
       </c>
       <c r="T60">
-        <v>1.118717337413444</v>
+        <v>1.142007683637723</v>
       </c>
       <c r="U60">
         <v>0.07190000000000001</v>
@@ -6245,7 +6245,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>2.64426050263252</v>
+        <v>2.59944252801163</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6253,22 +6253,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1254555562840449</v>
+        <v>0.1252401972380517</v>
       </c>
       <c r="C61">
-        <v>54.52214765772148</v>
+        <v>53.84332595232193</v>
       </c>
       <c r="D61">
-        <v>100.8419476577215</v>
+        <v>101.1153259523219</v>
       </c>
       <c r="E61">
-        <v>50.95979999999999</v>
+        <v>51.912</v>
       </c>
       <c r="F61">
-        <v>56.17979999999999</v>
+        <v>57.132</v>
       </c>
       <c r="G61">
         <v>9.859999999999999</v>
@@ -6289,28 +6289,28 @@
         <v>10.5</v>
       </c>
       <c r="M61">
-        <v>4.03932762</v>
+        <v>4.1077908</v>
       </c>
       <c r="N61">
-        <v>6.46067238</v>
+        <v>6.3922092</v>
       </c>
       <c r="O61">
-        <v>1.8735949902</v>
+        <v>1.853740668</v>
       </c>
       <c r="P61">
-        <v>4.5870773898</v>
+        <v>4.538468532</v>
       </c>
       <c r="Q61">
-        <v>8.4870773898</v>
+        <v>8.438468532</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.2325284055708412</v>
+        <v>0.2365269930951293</v>
       </c>
       <c r="T61">
-        <v>1.142007683637723</v>
+        <v>1.166462547173215</v>
       </c>
       <c r="U61">
         <v>0.07190000000000001</v>
@@ -6327,7 +6327,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>2.59944252801163</v>
+        <v>2.556118485878103</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6335,22 +6335,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1252401972380517</v>
+        <v>0.1250248381920586</v>
       </c>
       <c r="C62">
-        <v>53.84332595232193</v>
+        <v>53.16599051032316</v>
       </c>
       <c r="D62">
-        <v>101.1153259523219</v>
+        <v>101.3901905103232</v>
       </c>
       <c r="E62">
-        <v>51.912</v>
+        <v>52.8642</v>
       </c>
       <c r="F62">
-        <v>57.132</v>
+        <v>58.0842</v>
       </c>
       <c r="G62">
         <v>9.859999999999999</v>
@@ -6371,28 +6371,28 @@
         <v>10.5</v>
       </c>
       <c r="M62">
-        <v>4.1077908</v>
+        <v>4.17625398</v>
       </c>
       <c r="N62">
-        <v>6.3922092</v>
+        <v>6.32374602</v>
       </c>
       <c r="O62">
-        <v>1.853740668</v>
+        <v>1.8338863458</v>
       </c>
       <c r="P62">
-        <v>4.538468532</v>
+        <v>4.4898596742</v>
       </c>
       <c r="Q62">
-        <v>8.438468532</v>
+        <v>8.3898596742</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.2365269930951293</v>
+        <v>0.2407306363898938</v>
       </c>
       <c r="T62">
-        <v>1.166462547173215</v>
+        <v>1.19217150627463</v>
       </c>
       <c r="U62">
         <v>0.07190000000000001</v>
@@ -6409,7 +6409,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>2.556118485878103</v>
+        <v>2.514214904142396</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6417,22 +6417,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1250248381920586</v>
+        <v>0.1265262591460654</v>
       </c>
       <c r="C63">
-        <v>53.16599051032316</v>
+        <v>50.32804282210809</v>
       </c>
       <c r="D63">
-        <v>101.3901905103232</v>
+        <v>99.50444282210809</v>
       </c>
       <c r="E63">
-        <v>52.8642</v>
+        <v>53.8164</v>
       </c>
       <c r="F63">
-        <v>58.0842</v>
+        <v>59.0364</v>
       </c>
       <c r="G63">
         <v>9.859999999999999</v>
@@ -6453,45 +6453,45 @@
         <v>10.5</v>
       </c>
       <c r="M63">
-        <v>4.17625398</v>
+        <v>4.47495912</v>
       </c>
       <c r="N63">
-        <v>6.32374602</v>
+        <v>6.02504088</v>
       </c>
       <c r="O63">
-        <v>1.8338863458</v>
+        <v>1.7472618552</v>
       </c>
       <c r="P63">
-        <v>4.4898596742</v>
+        <v>4.2777790248</v>
       </c>
       <c r="Q63">
-        <v>8.3898596742</v>
+        <v>8.1777790248</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.2407306363898938</v>
+        <v>0.2451555240685931</v>
       </c>
       <c r="T63">
-        <v>1.19217150627463</v>
+        <v>1.219233568486646</v>
       </c>
       <c r="U63">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V63">
         <v>0.29</v>
       </c>
       <c r="W63">
-        <v>0.051049</v>
+        <v>0.053818</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y63">
-        <v>2.514214904142396</v>
+        <v>2.346390149816608</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6499,22 +6499,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1265262591460654</v>
+        <v>0.1263385901000723</v>
       </c>
       <c r="C64">
-        <v>50.32804282210809</v>
+        <v>49.60770563263529</v>
       </c>
       <c r="D64">
-        <v>99.50444282210809</v>
+        <v>99.73630563263529</v>
       </c>
       <c r="E64">
-        <v>53.8164</v>
+        <v>54.7686</v>
       </c>
       <c r="F64">
-        <v>59.0364</v>
+        <v>59.9886</v>
       </c>
       <c r="G64">
         <v>9.859999999999999</v>
@@ -6535,28 +6535,28 @@
         <v>10.5</v>
       </c>
       <c r="M64">
-        <v>4.47495912</v>
+        <v>4.54713588</v>
       </c>
       <c r="N64">
-        <v>6.02504088</v>
+        <v>5.95286412</v>
       </c>
       <c r="O64">
-        <v>1.7472618552</v>
+        <v>1.7263305948</v>
       </c>
       <c r="P64">
-        <v>4.2777790248</v>
+        <v>4.226533525200001</v>
       </c>
       <c r="Q64">
-        <v>8.1777790248</v>
+        <v>8.126533525200001</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.2451555240685931</v>
+        <v>0.2498195948650601</v>
       </c>
       <c r="T64">
-        <v>1.219233568486646</v>
+        <v>1.247758444872284</v>
       </c>
       <c r="U64">
         <v>0.07580000000000001</v>
@@ -6573,7 +6573,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>2.346390149816608</v>
+        <v>2.309145861724282</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6581,22 +6581,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1263385901000723</v>
+        <v>0.1261509210540791</v>
       </c>
       <c r="C65">
-        <v>49.60770563263529</v>
+        <v>48.8884515290036</v>
       </c>
       <c r="D65">
-        <v>99.73630563263529</v>
+        <v>99.9692515290036</v>
       </c>
       <c r="E65">
-        <v>54.7686</v>
+        <v>55.7208</v>
       </c>
       <c r="F65">
-        <v>59.9886</v>
+        <v>60.9408</v>
       </c>
       <c r="G65">
         <v>9.859999999999999</v>
@@ -6617,28 +6617,28 @@
         <v>10.5</v>
       </c>
       <c r="M65">
-        <v>4.54713588</v>
+        <v>4.61931264</v>
       </c>
       <c r="N65">
-        <v>5.95286412</v>
+        <v>5.88068736</v>
       </c>
       <c r="O65">
-        <v>1.7263305948</v>
+        <v>1.7053993344</v>
       </c>
       <c r="P65">
-        <v>4.226533525200001</v>
+        <v>4.1752880256</v>
       </c>
       <c r="Q65">
-        <v>8.126533525200001</v>
+        <v>8.075288025599999</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.2498195948650601</v>
+        <v>0.2547427807057752</v>
       </c>
       <c r="T65">
-        <v>1.247758444872284</v>
+        <v>1.27786803661268</v>
       </c>
       <c r="U65">
         <v>0.07580000000000001</v>
@@ -6655,7 +6655,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>2.309145861724282</v>
+        <v>2.27306545763484</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6663,22 +6663,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1261509210540791</v>
+        <v>0.1259632520080859</v>
       </c>
       <c r="C66">
-        <v>48.8884515290036</v>
+        <v>48.17028811800334</v>
       </c>
       <c r="D66">
-        <v>99.9692515290036</v>
+        <v>100.2032881180033</v>
       </c>
       <c r="E66">
-        <v>55.7208</v>
+        <v>56.673</v>
       </c>
       <c r="F66">
-        <v>60.9408</v>
+        <v>61.893</v>
       </c>
       <c r="G66">
         <v>9.859999999999999</v>
@@ -6699,28 +6699,28 @@
         <v>10.5</v>
       </c>
       <c r="M66">
-        <v>4.61931264</v>
+        <v>4.6914894</v>
       </c>
       <c r="N66">
-        <v>5.88068736</v>
+        <v>5.8085106</v>
       </c>
       <c r="O66">
-        <v>1.7053993344</v>
+        <v>1.684468074</v>
       </c>
       <c r="P66">
-        <v>4.1752880256</v>
+        <v>4.124042526</v>
       </c>
       <c r="Q66">
-        <v>8.075288025599999</v>
+        <v>8.024042526000001</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.2547427807057752</v>
+        <v>0.2599472914516741</v>
       </c>
       <c r="T66">
-        <v>1.27786803661268</v>
+        <v>1.309698176452528</v>
       </c>
       <c r="U66">
         <v>0.07580000000000001</v>
@@ -6737,7 +6737,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>2.27306545763484</v>
+        <v>2.238095219825073</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6745,22 +6745,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1259632520080859</v>
+        <v>0.1257755829620928</v>
       </c>
       <c r="C67">
-        <v>48.17028811800334</v>
+        <v>47.4532230778247</v>
       </c>
       <c r="D67">
-        <v>100.2032881180033</v>
+        <v>100.4384230778247</v>
       </c>
       <c r="E67">
-        <v>56.673</v>
+        <v>57.62520000000001</v>
       </c>
       <c r="F67">
-        <v>61.893</v>
+        <v>62.84520000000001</v>
       </c>
       <c r="G67">
         <v>9.859999999999999</v>
@@ -6781,28 +6781,28 @@
         <v>10.5</v>
       </c>
       <c r="M67">
-        <v>4.6914894</v>
+        <v>4.763666160000001</v>
       </c>
       <c r="N67">
-        <v>5.8085106</v>
+        <v>5.736333839999999</v>
       </c>
       <c r="O67">
-        <v>1.684468074</v>
+        <v>1.6635368136</v>
       </c>
       <c r="P67">
-        <v>4.124042526</v>
+        <v>4.0727970264</v>
       </c>
       <c r="Q67">
-        <v>8.024042526000001</v>
+        <v>7.9727970264</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.2599472914516741</v>
+        <v>0.2654579498885081</v>
       </c>
       <c r="T67">
-        <v>1.309698176452528</v>
+        <v>1.343400677459424</v>
       </c>
       <c r="U67">
         <v>0.07580000000000001</v>
@@ -6819,7 +6819,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>2.238095219825073</v>
+        <v>2.204184686191359</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6827,22 +6827,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1257755829620928</v>
+        <v>0.1255879139160996</v>
       </c>
       <c r="C68">
-        <v>47.4532230778247</v>
+        <v>46.73726415889741</v>
       </c>
       <c r="D68">
-        <v>100.4384230778247</v>
+        <v>100.6746641588974</v>
       </c>
       <c r="E68">
-        <v>57.62520000000001</v>
+        <v>58.5774</v>
       </c>
       <c r="F68">
-        <v>62.84520000000001</v>
+        <v>63.7974</v>
       </c>
       <c r="G68">
         <v>9.859999999999999</v>
@@ -6863,28 +6863,28 @@
         <v>10.5</v>
       </c>
       <c r="M68">
-        <v>4.763666160000001</v>
+        <v>4.835842920000001</v>
       </c>
       <c r="N68">
-        <v>5.736333839999999</v>
+        <v>5.664157079999999</v>
       </c>
       <c r="O68">
-        <v>1.6635368136</v>
+        <v>1.6426055532</v>
       </c>
       <c r="P68">
-        <v>4.0727970264</v>
+        <v>4.0215515268</v>
       </c>
       <c r="Q68">
-        <v>7.9727970264</v>
+        <v>7.9215515268</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.2654579498885081</v>
+        <v>0.2713025876245442</v>
       </c>
       <c r="T68">
-        <v>1.343400677459424</v>
+        <v>1.379145754284921</v>
       </c>
       <c r="U68">
         <v>0.07580000000000001</v>
@@ -6901,7 +6901,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>2.204184686191359</v>
+        <v>2.171286407292981</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6909,22 +6909,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1255879139160996</v>
+        <v>0.1254002448701065</v>
       </c>
       <c r="C69">
-        <v>46.73726415889741</v>
+        <v>46.02241918474198</v>
       </c>
       <c r="D69">
-        <v>100.6746641588974</v>
+        <v>100.912019184742</v>
       </c>
       <c r="E69">
-        <v>58.5774</v>
+        <v>59.5296</v>
       </c>
       <c r="F69">
-        <v>63.7974</v>
+        <v>64.7496</v>
       </c>
       <c r="G69">
         <v>9.859999999999999</v>
@@ -6945,28 +6945,28 @@
         <v>10.5</v>
       </c>
       <c r="M69">
-        <v>4.835842920000001</v>
+        <v>4.908019680000001</v>
       </c>
       <c r="N69">
-        <v>5.664157079999999</v>
+        <v>5.591980319999999</v>
       </c>
       <c r="O69">
-        <v>1.6426055532</v>
+        <v>1.6216742928</v>
       </c>
       <c r="P69">
-        <v>4.0215515268</v>
+        <v>3.970306027199999</v>
       </c>
       <c r="Q69">
-        <v>7.9215515268</v>
+        <v>7.8703060272</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.2713025876245442</v>
+        <v>0.2775125152190827</v>
       </c>
       <c r="T69">
-        <v>1.379145754284921</v>
+        <v>1.417124898412012</v>
       </c>
       <c r="U69">
         <v>0.07580000000000001</v>
@@ -6983,7 +6983,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>2.171286407292981</v>
+        <v>2.13935572483279</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6991,22 +6991,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1254002448701065</v>
+        <v>0.1252125758241133</v>
       </c>
       <c r="C70">
-        <v>46.02241918474198</v>
+        <v>45.30869605283387</v>
       </c>
       <c r="D70">
-        <v>100.912019184742</v>
+        <v>101.1504960528339</v>
       </c>
       <c r="E70">
-        <v>59.5296</v>
+        <v>60.48180000000001</v>
       </c>
       <c r="F70">
-        <v>64.7496</v>
+        <v>65.70180000000001</v>
       </c>
       <c r="G70">
         <v>9.859999999999999</v>
@@ -7027,28 +7027,28 @@
         <v>10.5</v>
       </c>
       <c r="M70">
-        <v>4.908019680000001</v>
+        <v>4.980196440000001</v>
       </c>
       <c r="N70">
-        <v>5.591980319999999</v>
+        <v>5.519803559999999</v>
       </c>
       <c r="O70">
-        <v>1.6216742928</v>
+        <v>1.6007430324</v>
       </c>
       <c r="P70">
-        <v>3.970306027199999</v>
+        <v>3.919060527599999</v>
       </c>
       <c r="Q70">
-        <v>7.8703060272</v>
+        <v>7.8190605276</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.2775125152190827</v>
+        <v>0.2841230833035913</v>
       </c>
       <c r="T70">
-        <v>1.417124898412012</v>
+        <v>1.45755430990214</v>
       </c>
       <c r="U70">
         <v>0.07580000000000001</v>
@@ -7065,7 +7065,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>2.13935572483279</v>
+        <v>2.108350569400431</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7073,22 +7073,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1252125758241133</v>
+        <v>0.1250249067781201</v>
       </c>
       <c r="C71">
-        <v>45.30869605283387</v>
+        <v>44.59610273547891</v>
       </c>
       <c r="D71">
-        <v>101.1504960528339</v>
+        <v>101.3901027354789</v>
       </c>
       <c r="E71">
-        <v>60.48180000000001</v>
+        <v>61.43400000000001</v>
       </c>
       <c r="F71">
-        <v>65.70180000000001</v>
+        <v>66.65400000000001</v>
       </c>
       <c r="G71">
         <v>9.859999999999999</v>
@@ -7109,28 +7109,28 @@
         <v>10.5</v>
       </c>
       <c r="M71">
-        <v>4.980196440000001</v>
+        <v>5.052373200000001</v>
       </c>
       <c r="N71">
-        <v>5.519803559999999</v>
+        <v>5.447626799999999</v>
       </c>
       <c r="O71">
-        <v>1.6007430324</v>
+        <v>1.579811772</v>
       </c>
       <c r="P71">
-        <v>3.919060527599999</v>
+        <v>3.867815028</v>
       </c>
       <c r="Q71">
-        <v>7.8190605276</v>
+        <v>7.767815028</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.2841230833035913</v>
+        <v>0.2911743559270671</v>
       </c>
       <c r="T71">
-        <v>1.45755430990214</v>
+        <v>1.500679015491611</v>
       </c>
       <c r="U71">
         <v>0.07580000000000001</v>
@@ -7147,7 +7147,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>2.108350569400431</v>
+        <v>2.078231275551853</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7155,22 +7155,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1250249067781201</v>
+        <v>0.124837237732127</v>
       </c>
       <c r="C72">
-        <v>44.59610273547891</v>
+        <v>43.88464728070208</v>
       </c>
       <c r="D72">
-        <v>101.3901027354789</v>
+        <v>101.6308472807021</v>
       </c>
       <c r="E72">
-        <v>61.43400000000001</v>
+        <v>62.3862</v>
       </c>
       <c r="F72">
-        <v>66.65400000000001</v>
+        <v>67.6062</v>
       </c>
       <c r="G72">
         <v>9.859999999999999</v>
@@ -7191,28 +7191,28 @@
         <v>10.5</v>
       </c>
       <c r="M72">
-        <v>5.052373200000001</v>
+        <v>5.12454996</v>
       </c>
       <c r="N72">
-        <v>5.447626799999999</v>
+        <v>5.37545004</v>
       </c>
       <c r="O72">
-        <v>1.579811772</v>
+        <v>1.5588805116</v>
       </c>
       <c r="P72">
-        <v>3.867815028</v>
+        <v>3.8165695284</v>
       </c>
       <c r="Q72">
-        <v>7.767815028</v>
+        <v>7.7165695284</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.2911743559270671</v>
+        <v>0.298711923214231</v>
       </c>
       <c r="T72">
-        <v>1.500679015491611</v>
+        <v>1.546777838707941</v>
       </c>
       <c r="U72">
         <v>0.07580000000000001</v>
@@ -7229,7 +7229,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>2.078231275551853</v>
+        <v>2.048960412515912</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7237,22 +7237,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.124837237732127</v>
+        <v>0.1246495686861338</v>
       </c>
       <c r="C73">
-        <v>43.88464728070211</v>
+        <v>43.17433781314836</v>
       </c>
       <c r="D73">
-        <v>101.6308472807021</v>
+        <v>101.8727378131483</v>
       </c>
       <c r="E73">
-        <v>62.3862</v>
+        <v>63.33839999999999</v>
       </c>
       <c r="F73">
-        <v>67.6062</v>
+        <v>68.55839999999999</v>
       </c>
       <c r="G73">
         <v>9.859999999999999</v>
@@ -7273,28 +7273,28 @@
         <v>10.5</v>
       </c>
       <c r="M73">
-        <v>5.12454996</v>
+        <v>5.19672672</v>
       </c>
       <c r="N73">
-        <v>5.37545004</v>
+        <v>5.30327328</v>
       </c>
       <c r="O73">
-        <v>1.5588805116</v>
+        <v>1.5379492512</v>
       </c>
       <c r="P73">
-        <v>3.8165695284</v>
+        <v>3.7653240288</v>
       </c>
       <c r="Q73">
-        <v>7.7165695284</v>
+        <v>7.665324028800001</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.2987119232142309</v>
+        <v>0.3067878881647636</v>
       </c>
       <c r="T73">
-        <v>1.546777838707941</v>
+        <v>1.596169435011152</v>
       </c>
       <c r="U73">
         <v>0.07580000000000001</v>
@@ -7311,7 +7311,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>2.048960412515912</v>
+        <v>2.020502629008746</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7319,22 +7319,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1246495686861338</v>
+        <v>0.1318217596401406</v>
       </c>
       <c r="C74">
-        <v>43.17433781314836</v>
+        <v>33.72834819921879</v>
       </c>
       <c r="D74">
-        <v>101.8727378131483</v>
+        <v>93.37894819921878</v>
       </c>
       <c r="E74">
-        <v>63.33839999999999</v>
+        <v>64.2906</v>
       </c>
       <c r="F74">
-        <v>68.55839999999999</v>
+        <v>69.5106</v>
       </c>
       <c r="G74">
         <v>9.859999999999999</v>
@@ -7355,45 +7355,45 @@
         <v>10.5</v>
       </c>
       <c r="M74">
-        <v>5.19672672</v>
+        <v>6.255953999999999</v>
       </c>
       <c r="N74">
-        <v>5.30327328</v>
+        <v>4.244046000000001</v>
       </c>
       <c r="O74">
-        <v>1.5379492512</v>
+        <v>1.23077334</v>
       </c>
       <c r="P74">
-        <v>3.7653240288</v>
+        <v>3.013272660000001</v>
       </c>
       <c r="Q74">
-        <v>7.665324028800001</v>
+        <v>6.913272660000001</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.3067878881647636</v>
+        <v>0.3154620727412616</v>
       </c>
       <c r="T74">
-        <v>1.596169435011152</v>
+        <v>1.649219668077563</v>
       </c>
       <c r="U74">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V74">
         <v>0.29</v>
       </c>
       <c r="W74">
-        <v>0.053818</v>
+        <v>0.0639</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y74">
-        <v>2.020502629008746</v>
+        <v>1.67840108798754</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7401,22 +7401,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.1318217596401406</v>
+        <v>0.1317349105941475</v>
       </c>
       <c r="C75">
-        <v>33.72834819921879</v>
+        <v>32.8705204690085</v>
       </c>
       <c r="D75">
-        <v>93.37894819921878</v>
+        <v>93.4733204690085</v>
       </c>
       <c r="E75">
-        <v>64.2906</v>
+        <v>65.2428</v>
       </c>
       <c r="F75">
-        <v>69.5106</v>
+        <v>70.4628</v>
       </c>
       <c r="G75">
         <v>9.859999999999999</v>
@@ -7437,28 +7437,28 @@
         <v>10.5</v>
       </c>
       <c r="M75">
-        <v>6.255953999999999</v>
+        <v>6.341652</v>
       </c>
       <c r="N75">
-        <v>4.244046000000001</v>
+        <v>4.158348</v>
       </c>
       <c r="O75">
-        <v>1.23077334</v>
+        <v>1.20592092</v>
       </c>
       <c r="P75">
-        <v>3.013272660000001</v>
+        <v>2.95242708</v>
       </c>
       <c r="Q75">
-        <v>6.913272660000001</v>
+        <v>6.85242708</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.3154620727412616</v>
+        <v>0.3248035022851826</v>
       </c>
       <c r="T75">
-        <v>1.649219668077563</v>
+        <v>1.70635068830293</v>
       </c>
       <c r="U75">
         <v>0.09</v>
@@ -7475,7 +7475,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>1.67840108798754</v>
+        <v>1.655719992203924</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7483,22 +7483,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.1317349105941475</v>
+        <v>0.1316480615481543</v>
       </c>
       <c r="C76">
-        <v>32.8705204690085</v>
+        <v>32.01288368409044</v>
       </c>
       <c r="D76">
-        <v>93.4733204690085</v>
+        <v>93.56788368409043</v>
       </c>
       <c r="E76">
-        <v>65.2428</v>
+        <v>66.19499999999999</v>
       </c>
       <c r="F76">
-        <v>70.4628</v>
+        <v>71.41499999999999</v>
       </c>
       <c r="G76">
         <v>9.859999999999999</v>
@@ -7519,28 +7519,28 @@
         <v>10.5</v>
       </c>
       <c r="M76">
-        <v>6.341652</v>
+        <v>6.427349999999999</v>
       </c>
       <c r="N76">
-        <v>4.158348</v>
+        <v>4.072650000000001</v>
       </c>
       <c r="O76">
-        <v>1.20592092</v>
+        <v>1.1810685</v>
       </c>
       <c r="P76">
-        <v>2.95242708</v>
+        <v>2.891581500000001</v>
       </c>
       <c r="Q76">
-        <v>6.85242708</v>
+        <v>6.791581500000001</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.3248035022851826</v>
+        <v>0.3348922461926173</v>
       </c>
       <c r="T76">
-        <v>1.70635068830293</v>
+        <v>1.768052190146326</v>
       </c>
       <c r="U76">
         <v>0.09</v>
@@ -7557,7 +7557,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>1.655719992203924</v>
+        <v>1.633643725641206</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7565,22 +7565,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.1316480615481543</v>
+        <v>0.1315612125021612</v>
       </c>
       <c r="C77">
-        <v>32.01288368409044</v>
+        <v>31.15543842456658</v>
       </c>
       <c r="D77">
-        <v>93.56788368409043</v>
+        <v>93.66263842456658</v>
       </c>
       <c r="E77">
-        <v>66.19499999999999</v>
+        <v>67.1472</v>
       </c>
       <c r="F77">
-        <v>71.41499999999999</v>
+        <v>72.3672</v>
       </c>
       <c r="G77">
         <v>9.859999999999999</v>
@@ -7601,28 +7601,28 @@
         <v>10.5</v>
       </c>
       <c r="M77">
-        <v>6.427349999999999</v>
+        <v>6.513048</v>
       </c>
       <c r="N77">
-        <v>4.072650000000001</v>
+        <v>3.986952</v>
       </c>
       <c r="O77">
-        <v>1.1810685</v>
+        <v>1.15621608</v>
       </c>
       <c r="P77">
-        <v>2.891581500000001</v>
+        <v>2.83073592</v>
       </c>
       <c r="Q77">
-        <v>6.791581500000001</v>
+        <v>6.730735920000001</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.3348922461926173</v>
+        <v>0.3458217187590049</v>
       </c>
       <c r="T77">
-        <v>1.768052190146326</v>
+        <v>1.834895483810006</v>
       </c>
       <c r="U77">
         <v>0.09</v>
@@ -7639,7 +7639,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>1.633643725641206</v>
+        <v>1.612148413461716</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7647,22 +7647,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.1315612125021612</v>
+        <v>0.131474363456168</v>
       </c>
       <c r="C78">
-        <v>31.15543842456658</v>
+        <v>30.29818527289116</v>
       </c>
       <c r="D78">
-        <v>93.66263842456658</v>
+        <v>93.75758527289116</v>
       </c>
       <c r="E78">
-        <v>67.1472</v>
+        <v>68.0994</v>
       </c>
       <c r="F78">
-        <v>72.3672</v>
+        <v>73.3194</v>
       </c>
       <c r="G78">
         <v>9.859999999999999</v>
@@ -7683,28 +7683,28 @@
         <v>10.5</v>
       </c>
       <c r="M78">
-        <v>6.513048</v>
+        <v>6.598746</v>
       </c>
       <c r="N78">
-        <v>3.986952</v>
+        <v>3.901254</v>
       </c>
       <c r="O78">
-        <v>1.15621608</v>
+        <v>1.13136366</v>
       </c>
       <c r="P78">
-        <v>2.83073592</v>
+        <v>2.76989034</v>
       </c>
       <c r="Q78">
-        <v>6.730735920000001</v>
+        <v>6.66989034</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.3458217187590049</v>
+        <v>0.3577015802442087</v>
       </c>
       <c r="T78">
-        <v>1.834895483810006</v>
+        <v>1.907551237792265</v>
       </c>
       <c r="U78">
         <v>0.09</v>
@@ -7721,7 +7721,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>1.612148413461716</v>
+        <v>1.591211421079096</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7729,22 +7729,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.131474363456168</v>
+        <v>0.1313875144101748</v>
       </c>
       <c r="C79">
-        <v>30.29818527289116</v>
+        <v>29.44112481388248</v>
       </c>
       <c r="D79">
-        <v>93.75758527289116</v>
+        <v>93.85272481388249</v>
       </c>
       <c r="E79">
-        <v>68.0994</v>
+        <v>69.05160000000001</v>
       </c>
       <c r="F79">
-        <v>73.3194</v>
+        <v>74.27160000000001</v>
       </c>
       <c r="G79">
         <v>9.859999999999999</v>
@@ -7765,28 +7765,28 @@
         <v>10.5</v>
       </c>
       <c r="M79">
-        <v>6.598746</v>
+        <v>6.684444</v>
       </c>
       <c r="N79">
-        <v>3.901254</v>
+        <v>3.815556</v>
       </c>
       <c r="O79">
-        <v>1.13136366</v>
+        <v>1.10651124</v>
       </c>
       <c r="P79">
-        <v>2.76989034</v>
+        <v>2.70904476</v>
       </c>
       <c r="Q79">
-        <v>6.66989034</v>
+        <v>6.609044760000001</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.3577015802442087</v>
+        <v>0.3706614291371584</v>
       </c>
       <c r="T79">
-        <v>1.907551237792265</v>
+        <v>1.986812060318367</v>
       </c>
       <c r="U79">
         <v>0.09</v>
@@ -7803,7 +7803,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>1.591211421079096</v>
+        <v>1.570811274655005</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7811,22 +7811,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.1313875144101748</v>
+        <v>0.1313006653641817</v>
       </c>
       <c r="C80">
-        <v>29.44112481388248</v>
+        <v>28.58425763473515</v>
       </c>
       <c r="D80">
-        <v>93.85272481388249</v>
+        <v>93.94805763473515</v>
       </c>
       <c r="E80">
-        <v>69.05160000000001</v>
+        <v>70.0038</v>
       </c>
       <c r="F80">
-        <v>74.27160000000001</v>
+        <v>75.2238</v>
       </c>
       <c r="G80">
         <v>9.859999999999999</v>
@@ -7847,28 +7847,28 @@
         <v>10.5</v>
       </c>
       <c r="M80">
-        <v>6.684444</v>
+        <v>6.770142</v>
       </c>
       <c r="N80">
-        <v>3.815556</v>
+        <v>3.729858</v>
       </c>
       <c r="O80">
-        <v>1.10651124</v>
+        <v>1.08165882</v>
       </c>
       <c r="P80">
-        <v>2.70904476</v>
+        <v>2.64819918</v>
       </c>
       <c r="Q80">
-        <v>6.609044760000001</v>
+        <v>6.548199180000001</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.3706614291371584</v>
+        <v>0.3848555493532462</v>
       </c>
       <c r="T80">
-        <v>1.986812060318367</v>
+        <v>2.073621532608859</v>
       </c>
       <c r="U80">
         <v>0.09</v>
@@ -7885,7 +7885,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>1.570811274655005</v>
+        <v>1.550927587634056</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7893,22 +7893,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.1313006653641817</v>
+        <v>0.1312138163181885</v>
       </c>
       <c r="C81">
-        <v>28.58425763473515</v>
+        <v>27.72758432503184</v>
       </c>
       <c r="D81">
-        <v>93.94805763473515</v>
+        <v>94.04358432503184</v>
       </c>
       <c r="E81">
-        <v>70.0038</v>
+        <v>70.956</v>
       </c>
       <c r="F81">
-        <v>75.2238</v>
+        <v>76.176</v>
       </c>
       <c r="G81">
         <v>9.859999999999999</v>
@@ -7929,28 +7929,28 @@
         <v>10.5</v>
       </c>
       <c r="M81">
-        <v>6.770142</v>
+        <v>6.85584</v>
       </c>
       <c r="N81">
-        <v>3.729858</v>
+        <v>3.64416</v>
       </c>
       <c r="O81">
-        <v>1.08165882</v>
+        <v>1.0568064</v>
       </c>
       <c r="P81">
-        <v>2.64819918</v>
+        <v>2.5873536</v>
       </c>
       <c r="Q81">
-        <v>6.548199180000001</v>
+        <v>6.4873536</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.3848555493532462</v>
+        <v>0.4004690815909427</v>
       </c>
       <c r="T81">
-        <v>2.073621532608859</v>
+        <v>2.169111952128401</v>
       </c>
       <c r="U81">
         <v>0.09</v>
@@ -7967,7 +7967,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>1.550927587634056</v>
+        <v>1.53154099278863</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7975,22 +7975,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.1312138163181885</v>
+        <v>0.1311269672721954</v>
       </c>
       <c r="C82">
-        <v>27.72758432503184</v>
+        <v>26.87110547675577</v>
       </c>
       <c r="D82">
-        <v>94.04358432503184</v>
+        <v>94.13930547675578</v>
       </c>
       <c r="E82">
-        <v>70.956</v>
+        <v>71.90820000000001</v>
       </c>
       <c r="F82">
-        <v>76.176</v>
+        <v>77.12820000000001</v>
       </c>
       <c r="G82">
         <v>9.859999999999999</v>
@@ -8011,28 +8011,28 @@
         <v>10.5</v>
       </c>
       <c r="M82">
-        <v>6.85584</v>
+        <v>6.941538</v>
       </c>
       <c r="N82">
-        <v>3.64416</v>
+        <v>3.558462</v>
       </c>
       <c r="O82">
-        <v>1.0568064</v>
+        <v>1.03195398</v>
       </c>
       <c r="P82">
-        <v>2.5873536</v>
+        <v>2.52650802</v>
       </c>
       <c r="Q82">
-        <v>6.4873536</v>
+        <v>6.42650802</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.4004690815909427</v>
+        <v>0.4177261435378704</v>
       </c>
       <c r="T82">
-        <v>2.169111952128401</v>
+        <v>2.274653994755262</v>
       </c>
       <c r="U82">
         <v>0.09</v>
@@ -8049,7 +8049,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>1.53154099278863</v>
+        <v>1.512633079297412</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8057,22 +8057,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.1311269672721954</v>
+        <v>0.1688832940716988</v>
       </c>
       <c r="C83">
-        <v>26.87110547675577</v>
+        <v>-2.95872904761913</v>
       </c>
       <c r="D83">
-        <v>94.13930547675578</v>
+        <v>65.26167095238088</v>
       </c>
       <c r="E83">
-        <v>71.90820000000001</v>
+        <v>72.86040000000001</v>
       </c>
       <c r="F83">
-        <v>77.12820000000001</v>
+        <v>78.08040000000001</v>
       </c>
       <c r="G83">
         <v>9.859999999999999</v>
@@ -8093,45 +8093,45 @@
         <v>10.5</v>
       </c>
       <c r="M83">
-        <v>6.941538</v>
+        <v>11.46220272</v>
       </c>
       <c r="N83">
-        <v>3.558462</v>
+        <v>-0.9622027200000023</v>
       </c>
       <c r="O83">
-        <v>1.03195398</v>
+        <v>-0.2790387888000007</v>
       </c>
       <c r="P83">
-        <v>2.52650802</v>
+        <v>-0.6831639312000016</v>
       </c>
       <c r="Q83">
-        <v>6.42650802</v>
+        <v>3.216836068799999</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.4177261435378704</v>
+        <v>0.4471437222284747</v>
       </c>
       <c r="T83">
-        <v>2.274653994755262</v>
+        <v>2.454568243987911</v>
       </c>
       <c r="U83">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V83">
-        <v>0.29</v>
+        <v>0.2656557447450205</v>
       </c>
       <c r="W83">
-        <v>0.0639</v>
+        <v>0.107801736671431</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y83">
-        <v>1.512633079297412</v>
+        <v>0.9160542922242085</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8139,22 +8139,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.1688832940716988</v>
+        <v>0.1698932940716989</v>
       </c>
       <c r="C84">
-        <v>-2.95872904761913</v>
+        <v>-4.442096248514133</v>
       </c>
       <c r="D84">
-        <v>65.26167095238088</v>
+        <v>64.73050375148587</v>
       </c>
       <c r="E84">
-        <v>72.86040000000001</v>
+        <v>73.8126</v>
       </c>
       <c r="F84">
-        <v>78.08040000000001</v>
+        <v>79.0326</v>
       </c>
       <c r="G84">
         <v>9.859999999999999</v>
@@ -8175,37 +8175,37 @@
         <v>10.5</v>
       </c>
       <c r="M84">
-        <v>11.46220272</v>
+        <v>11.60198568</v>
       </c>
       <c r="N84">
-        <v>-0.9622027200000023</v>
+        <v>-1.101985680000002</v>
       </c>
       <c r="O84">
-        <v>-0.2790387888000007</v>
+        <v>-0.3195758472000006</v>
       </c>
       <c r="P84">
-        <v>-0.6831639312000016</v>
+        <v>-0.7824098328000015</v>
       </c>
       <c r="Q84">
-        <v>3.216836068799999</v>
+        <v>3.117590167199999</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.4471437222284747</v>
+        <v>0.4707521764772086</v>
       </c>
       <c r="T84">
-        <v>2.454568243987911</v>
+        <v>2.598954611281318</v>
       </c>
       <c r="U84">
         <v>0.1468</v>
       </c>
       <c r="V84">
-        <v>0.2656557447450205</v>
+        <v>0.2624550731215865</v>
       </c>
       <c r="W84">
-        <v>0.107801736671431</v>
+        <v>0.1082715952657511</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8213,7 +8213,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.9160542922242085</v>
+        <v>0.9050174935227121</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8221,22 +8221,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.1698932940716989</v>
+        <v>0.1709032940716989</v>
       </c>
       <c r="C85">
-        <v>-4.442096248514133</v>
+        <v>-5.91688687471725</v>
       </c>
       <c r="D85">
-        <v>64.73050375148587</v>
+        <v>64.20791312528276</v>
       </c>
       <c r="E85">
-        <v>73.8126</v>
+        <v>74.76480000000001</v>
       </c>
       <c r="F85">
-        <v>79.0326</v>
+        <v>79.98480000000001</v>
       </c>
       <c r="G85">
         <v>9.859999999999999</v>
@@ -8257,37 +8257,37 @@
         <v>10.5</v>
       </c>
       <c r="M85">
-        <v>11.60198568</v>
+        <v>11.74176864</v>
       </c>
       <c r="N85">
-        <v>-1.101985680000002</v>
+        <v>-1.241768640000002</v>
       </c>
       <c r="O85">
-        <v>-0.3195758472000006</v>
+        <v>-0.3601129056000005</v>
       </c>
       <c r="P85">
-        <v>-0.7824098328000015</v>
+        <v>-0.8816557344000013</v>
       </c>
       <c r="Q85">
-        <v>3.117590167199999</v>
+        <v>3.018344265599999</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.4707521764772086</v>
+        <v>0.4973116875070343</v>
       </c>
       <c r="T85">
-        <v>2.598954611281318</v>
+        <v>2.761389274486401</v>
       </c>
       <c r="U85">
         <v>0.1468</v>
       </c>
       <c r="V85">
-        <v>0.2624550731215865</v>
+        <v>0.2593306079653771</v>
       </c>
       <c r="W85">
-        <v>0.1082715952657511</v>
+        <v>0.1087302667506826</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8295,7 +8295,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.9050174935227121</v>
+        <v>0.8942434757426798</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8303,22 +8303,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.1709032940716989</v>
+        <v>0.1719132940716989</v>
       </c>
       <c r="C86">
-        <v>-5.916886874717235</v>
+        <v>-7.383306987147776</v>
       </c>
       <c r="D86">
-        <v>64.20791312528276</v>
+        <v>63.69369301285221</v>
       </c>
       <c r="E86">
-        <v>74.76479999999999</v>
+        <v>75.717</v>
       </c>
       <c r="F86">
-        <v>79.98479999999999</v>
+        <v>80.937</v>
       </c>
       <c r="G86">
         <v>9.859999999999999</v>
@@ -8339,37 +8339,37 @@
         <v>10.5</v>
       </c>
       <c r="M86">
-        <v>11.74176864</v>
+        <v>11.8815516</v>
       </c>
       <c r="N86">
-        <v>-1.24176864</v>
+        <v>-1.3815516</v>
       </c>
       <c r="O86">
-        <v>-0.3601129056</v>
+        <v>-0.4006499639999999</v>
       </c>
       <c r="P86">
-        <v>-0.8816557344000001</v>
+        <v>-0.980901636</v>
       </c>
       <c r="Q86">
-        <v>3.0183442656</v>
+        <v>2.919098364</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.4973116875070339</v>
+        <v>0.5274124666741695</v>
       </c>
       <c r="T86">
-        <v>2.761389274486399</v>
+        <v>2.945481892785493</v>
       </c>
       <c r="U86">
         <v>0.1468</v>
       </c>
       <c r="V86">
-        <v>0.2593306079653772</v>
+        <v>0.2562796596363727</v>
       </c>
       <c r="W86">
-        <v>0.1087302667506826</v>
+        <v>0.1091781459653805</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.8942434757426799</v>
+        <v>0.8837229642633543</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8385,22 +8385,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.1719132940716989</v>
+        <v>0.1729232940716989</v>
       </c>
       <c r="C87">
-        <v>-7.383306987147776</v>
+        <v>-8.841556098073909</v>
       </c>
       <c r="D87">
-        <v>63.69369301285221</v>
+        <v>63.18764390192609</v>
       </c>
       <c r="E87">
-        <v>75.717</v>
+        <v>76.6692</v>
       </c>
       <c r="F87">
-        <v>80.937</v>
+        <v>81.8892</v>
       </c>
       <c r="G87">
         <v>9.859999999999999</v>
@@ -8421,37 +8421,37 @@
         <v>10.5</v>
       </c>
       <c r="M87">
-        <v>11.8815516</v>
+        <v>12.02133456</v>
       </c>
       <c r="N87">
-        <v>-1.3815516</v>
+        <v>-1.521334560000001</v>
       </c>
       <c r="O87">
-        <v>-0.4006499639999999</v>
+        <v>-0.4411870224000004</v>
       </c>
       <c r="P87">
-        <v>-0.980901636</v>
+        <v>-1.080147537600001</v>
       </c>
       <c r="Q87">
-        <v>2.919098364</v>
+        <v>2.819852462399999</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.5274124666741695</v>
+        <v>0.5618133571508959</v>
       </c>
       <c r="T87">
-        <v>2.945481892785493</v>
+        <v>3.155873456555885</v>
       </c>
       <c r="U87">
         <v>0.1468</v>
       </c>
       <c r="V87">
-        <v>0.2562796596363727</v>
+        <v>0.2532996635940893</v>
       </c>
       <c r="W87">
-        <v>0.1091781459653805</v>
+        <v>0.1096156093843877</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8459,7 +8459,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.8837229642633543</v>
+        <v>0.8734471158416872</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8467,22 +8467,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.1729232940716989</v>
+        <v>0.1739332940716989</v>
       </c>
       <c r="C88">
-        <v>-8.841556098073909</v>
+        <v>-10.29182742920842</v>
       </c>
       <c r="D88">
-        <v>63.18764390192609</v>
+        <v>62.68957257079157</v>
       </c>
       <c r="E88">
-        <v>76.6692</v>
+        <v>77.62139999999999</v>
       </c>
       <c r="F88">
-        <v>81.8892</v>
+        <v>82.84139999999999</v>
       </c>
       <c r="G88">
         <v>9.859999999999999</v>
@@ -8503,37 +8503,37 @@
         <v>10.5</v>
       </c>
       <c r="M88">
-        <v>12.02133456</v>
+        <v>12.16111752</v>
       </c>
       <c r="N88">
-        <v>-1.521334560000001</v>
+        <v>-1.661117519999999</v>
       </c>
       <c r="O88">
-        <v>-0.4411870224000004</v>
+        <v>-0.4817240807999998</v>
       </c>
       <c r="P88">
-        <v>-1.080147537600001</v>
+        <v>-1.1793934392</v>
       </c>
       <c r="Q88">
-        <v>2.819852462399999</v>
+        <v>2.720606560800001</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.5618133571508959</v>
+        <v>0.6015066923163495</v>
       </c>
       <c r="T88">
-        <v>3.155873456555885</v>
+        <v>3.39863295321403</v>
       </c>
       <c r="U88">
         <v>0.1468</v>
       </c>
       <c r="V88">
-        <v>0.2532996635940893</v>
+        <v>0.2503881732079504</v>
       </c>
       <c r="W88">
-        <v>0.1096156093843877</v>
+        <v>0.1100430161730729</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8541,7 +8541,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.8734471158416872</v>
+        <v>0.8634074938205186</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8549,22 +8549,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.1739332940716989</v>
+        <v>0.1749432940716988</v>
       </c>
       <c r="C89">
-        <v>-10.29182742920842</v>
+        <v>-11.73430815769402</v>
       </c>
       <c r="D89">
-        <v>62.68957257079157</v>
+        <v>62.19929184230599</v>
       </c>
       <c r="E89">
-        <v>77.62139999999999</v>
+        <v>78.5736</v>
       </c>
       <c r="F89">
-        <v>82.84139999999999</v>
+        <v>83.7936</v>
       </c>
       <c r="G89">
         <v>9.859999999999999</v>
@@ -8585,37 +8585,37 @@
         <v>10.5</v>
       </c>
       <c r="M89">
-        <v>12.16111752</v>
+        <v>12.30090048</v>
       </c>
       <c r="N89">
-        <v>-1.661117519999999</v>
+        <v>-1.800900480000001</v>
       </c>
       <c r="O89">
-        <v>-0.4817240807999998</v>
+        <v>-0.5222611392000003</v>
       </c>
       <c r="P89">
-        <v>-1.1793934392</v>
+        <v>-1.278639340800001</v>
       </c>
       <c r="Q89">
-        <v>2.720606560800001</v>
+        <v>2.6213606592</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.6015066923163495</v>
+        <v>0.6478155833427119</v>
       </c>
       <c r="T89">
-        <v>3.39863295321403</v>
+        <v>3.681852365981867</v>
       </c>
       <c r="U89">
         <v>0.1468</v>
       </c>
       <c r="V89">
-        <v>0.2503881732079504</v>
+        <v>0.24754285305786</v>
       </c>
       <c r="W89">
-        <v>0.1100430161730729</v>
+        <v>0.1104607091711061</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8623,7 +8623,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.8634074938205186</v>
+        <v>0.8535960450271035</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8631,22 +8631,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.1749432940716988</v>
+        <v>0.1759532940716989</v>
       </c>
       <c r="C90">
-        <v>-11.73430815769402</v>
+        <v>-13.16917965063465</v>
       </c>
       <c r="D90">
-        <v>62.19929184230599</v>
+        <v>61.71662034936535</v>
       </c>
       <c r="E90">
-        <v>78.5736</v>
+        <v>79.5258</v>
       </c>
       <c r="F90">
-        <v>83.7936</v>
+        <v>84.7458</v>
       </c>
       <c r="G90">
         <v>9.859999999999999</v>
@@ -8667,37 +8667,37 @@
         <v>10.5</v>
       </c>
       <c r="M90">
-        <v>12.30090048</v>
+        <v>12.44068344</v>
       </c>
       <c r="N90">
-        <v>-1.800900480000001</v>
+        <v>-1.940683440000001</v>
       </c>
       <c r="O90">
-        <v>-0.5222611392000003</v>
+        <v>-0.5627981976000002</v>
       </c>
       <c r="P90">
-        <v>-1.278639340800001</v>
+        <v>-1.377885242400001</v>
       </c>
       <c r="Q90">
-        <v>2.6213606592</v>
+        <v>2.5221147576</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.6478155833427119</v>
+        <v>0.7025442727375041</v>
       </c>
       <c r="T90">
-        <v>3.681852365981867</v>
+        <v>4.016566217434764</v>
       </c>
       <c r="U90">
         <v>0.1468</v>
       </c>
       <c r="V90">
-        <v>0.24754285305786</v>
+        <v>0.2447614726864234</v>
       </c>
       <c r="W90">
-        <v>0.1104607091711061</v>
+        <v>0.1108690158096331</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8705,7 +8705,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.8535960450271035</v>
+        <v>0.8440050782290462</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8713,22 +8713,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.1759532940716989</v>
+        <v>0.1769632940716989</v>
       </c>
       <c r="C91">
-        <v>-13.16917965063465</v>
+        <v>-14.59661768879178</v>
       </c>
       <c r="D91">
-        <v>61.71662034936535</v>
+        <v>61.24138231120823</v>
       </c>
       <c r="E91">
-        <v>79.5258</v>
+        <v>80.47800000000001</v>
       </c>
       <c r="F91">
-        <v>84.7458</v>
+        <v>85.69800000000001</v>
       </c>
       <c r="G91">
         <v>9.859999999999999</v>
@@ -8749,37 +8749,37 @@
         <v>10.5</v>
       </c>
       <c r="M91">
-        <v>12.44068344</v>
+        <v>12.5804664</v>
       </c>
       <c r="N91">
-        <v>-1.940683440000001</v>
+        <v>-2.080466400000002</v>
       </c>
       <c r="O91">
-        <v>-0.5627981976000002</v>
+        <v>-0.6033352560000006</v>
       </c>
       <c r="P91">
-        <v>-1.377885242400001</v>
+        <v>-1.477131144000002</v>
       </c>
       <c r="Q91">
-        <v>2.5221147576</v>
+        <v>2.422868855999999</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.7025442727375041</v>
+        <v>0.7682187000112545</v>
       </c>
       <c r="T91">
-        <v>4.016566217434764</v>
+        <v>4.418222839178241</v>
       </c>
       <c r="U91">
         <v>0.1468</v>
       </c>
       <c r="V91">
-        <v>0.2447614726864234</v>
+        <v>0.2420419007676853</v>
       </c>
       <c r="W91">
-        <v>0.1108690158096331</v>
+        <v>0.1112682489673038</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8787,7 +8787,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.8440050782290462</v>
+        <v>0.8346272440265011</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8795,22 +8795,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.1769632940716989</v>
+        <v>0.1779732940716988</v>
       </c>
       <c r="C92">
-        <v>-14.59661768879178</v>
+        <v>-16.01679268002384</v>
       </c>
       <c r="D92">
-        <v>61.24138231120823</v>
+        <v>60.77340731997616</v>
       </c>
       <c r="E92">
-        <v>80.47800000000001</v>
+        <v>81.4302</v>
       </c>
       <c r="F92">
-        <v>85.69800000000001</v>
+        <v>86.6502</v>
       </c>
       <c r="G92">
         <v>9.859999999999999</v>
@@ -8831,37 +8831,37 @@
         <v>10.5</v>
       </c>
       <c r="M92">
-        <v>12.5804664</v>
+        <v>12.72024936</v>
       </c>
       <c r="N92">
-        <v>-2.080466400000002</v>
+        <v>-2.22024936</v>
       </c>
       <c r="O92">
-        <v>-0.6033352560000006</v>
+        <v>-0.6438723144</v>
       </c>
       <c r="P92">
-        <v>-1.477131144000002</v>
+        <v>-1.5763770456</v>
       </c>
       <c r="Q92">
-        <v>2.422868855999999</v>
+        <v>2.3236229544</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.7682187000112545</v>
+        <v>0.8484874444569493</v>
       </c>
       <c r="T92">
-        <v>4.418222839178241</v>
+        <v>4.909136487975823</v>
       </c>
       <c r="U92">
         <v>0.1468</v>
       </c>
       <c r="V92">
-        <v>0.2420419007676853</v>
+        <v>0.2393820996603482</v>
       </c>
       <c r="W92">
-        <v>0.1112682489673038</v>
+        <v>0.1116587077698609</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8869,7 +8869,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.8346272440265011</v>
+        <v>0.8254555160701661</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8877,22 +8877,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.1779732940716988</v>
+        <v>0.1789832940716989</v>
       </c>
       <c r="C93">
-        <v>-16.01679268002384</v>
+        <v>-17.4298698630145</v>
       </c>
       <c r="D93">
-        <v>60.77340731997616</v>
+        <v>60.31253013698551</v>
       </c>
       <c r="E93">
-        <v>81.4302</v>
+        <v>82.3824</v>
       </c>
       <c r="F93">
-        <v>86.6502</v>
+        <v>87.6024</v>
       </c>
       <c r="G93">
         <v>9.859999999999999</v>
@@ -8913,37 +8913,37 @@
         <v>10.5</v>
       </c>
       <c r="M93">
-        <v>12.72024936</v>
+        <v>12.86003232</v>
       </c>
       <c r="N93">
-        <v>-2.22024936</v>
+        <v>-2.360032320000002</v>
       </c>
       <c r="O93">
-        <v>-0.6438723144</v>
+        <v>-0.6844093728000005</v>
       </c>
       <c r="P93">
-        <v>-1.5763770456</v>
+        <v>-1.675622947200001</v>
       </c>
       <c r="Q93">
-        <v>2.3236229544</v>
+        <v>2.224377052799999</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.8484874444569493</v>
+        <v>0.9488233750140687</v>
       </c>
       <c r="T93">
-        <v>4.909136487975823</v>
+        <v>5.522778548972804</v>
       </c>
       <c r="U93">
         <v>0.1468</v>
       </c>
       <c r="V93">
-        <v>0.2393820996603482</v>
+        <v>0.2367801203162139</v>
       </c>
       <c r="W93">
-        <v>0.1116587077698609</v>
+        <v>0.1120406783375798</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8951,7 +8951,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.8254555160701661</v>
+        <v>0.8164831735041859</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8959,22 +8959,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.1789832940716989</v>
+        <v>0.1799932940716989</v>
       </c>
       <c r="C94">
-        <v>-17.4298698630145</v>
+        <v>-18.83600950180009</v>
       </c>
       <c r="D94">
-        <v>60.31253013698551</v>
+        <v>59.85859049819992</v>
       </c>
       <c r="E94">
-        <v>82.3824</v>
+        <v>83.33460000000001</v>
       </c>
       <c r="F94">
-        <v>87.6024</v>
+        <v>88.55460000000001</v>
       </c>
       <c r="G94">
         <v>9.859999999999999</v>
@@ -8995,37 +8995,37 @@
         <v>10.5</v>
       </c>
       <c r="M94">
-        <v>12.86003232</v>
+        <v>12.99981528</v>
       </c>
       <c r="N94">
-        <v>-2.360032320000002</v>
+        <v>-2.499815280000002</v>
       </c>
       <c r="O94">
-        <v>-0.6844093728000005</v>
+        <v>-0.7249464312000005</v>
       </c>
       <c r="P94">
-        <v>-1.675622947200001</v>
+        <v>-1.774868848800001</v>
       </c>
       <c r="Q94">
-        <v>2.224377052799999</v>
+        <v>2.125131151199999</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.9488233750140687</v>
+        <v>1.077826714301793</v>
       </c>
       <c r="T94">
-        <v>5.522778548972804</v>
+        <v>6.311746913111775</v>
       </c>
       <c r="U94">
         <v>0.1468</v>
       </c>
       <c r="V94">
-        <v>0.2367801203162139</v>
+        <v>0.2342340975171148</v>
       </c>
       <c r="W94">
-        <v>0.1120406783375798</v>
+        <v>0.1124144344844875</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9033,7 +9033,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.8164831735041859</v>
+        <v>0.8077037845417754</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9041,22 +9041,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.1799932940716989</v>
+        <v>0.2371740160827141</v>
       </c>
       <c r="C95">
-        <v>-18.83600950180009</v>
+        <v>-37.67338269986585</v>
       </c>
       <c r="D95">
-        <v>59.85859049819992</v>
+        <v>41.97341730013414</v>
       </c>
       <c r="E95">
-        <v>83.33460000000001</v>
+        <v>84.2868</v>
       </c>
       <c r="F95">
-        <v>88.55460000000001</v>
+        <v>89.5068</v>
       </c>
       <c r="G95">
         <v>9.859999999999999</v>
@@ -9077,45 +9077,45 @@
         <v>10.5</v>
       </c>
       <c r="M95">
-        <v>12.99981528</v>
+        <v>17.97296544</v>
       </c>
       <c r="N95">
-        <v>-2.499815280000002</v>
+        <v>-7.472965439999999</v>
       </c>
       <c r="O95">
-        <v>-0.7249464312000005</v>
+        <v>-2.1671599776</v>
       </c>
       <c r="P95">
-        <v>-1.774868848800001</v>
+        <v>-5.3058054624</v>
       </c>
       <c r="Q95">
-        <v>2.125131151199999</v>
+        <v>-1.405805462399999</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>1.077826714301793</v>
+        <v>1.340009866869012</v>
       </c>
       <c r="T95">
-        <v>6.311746913111775</v>
+        <v>7.915226436416192</v>
       </c>
       <c r="U95">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V95">
-        <v>0.2342340975171148</v>
+        <v>0.1694211236406851</v>
       </c>
       <c r="W95">
-        <v>0.1124144344844875</v>
+        <v>0.1667802383729504</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y95">
-        <v>0.8077037845417754</v>
+        <v>0.5842107711747762</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9123,22 +9123,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2371740160827141</v>
+        <v>0.2387240160827141</v>
       </c>
       <c r="C96">
-        <v>-37.67338269986585</v>
+        <v>-38.96280767649767</v>
       </c>
       <c r="D96">
-        <v>41.97341730013414</v>
+        <v>41.63619232350234</v>
       </c>
       <c r="E96">
-        <v>84.2868</v>
+        <v>85.239</v>
       </c>
       <c r="F96">
-        <v>89.5068</v>
+        <v>90.459</v>
       </c>
       <c r="G96">
         <v>9.859999999999999</v>
@@ -9159,37 +9159,37 @@
         <v>10.5</v>
       </c>
       <c r="M96">
-        <v>17.97296544</v>
+        <v>18.1641672</v>
       </c>
       <c r="N96">
-        <v>-7.472965439999999</v>
+        <v>-7.664167200000001</v>
       </c>
       <c r="O96">
-        <v>-2.1671599776</v>
+        <v>-2.222608488</v>
       </c>
       <c r="P96">
-        <v>-5.3058054624</v>
+        <v>-5.441558712000001</v>
       </c>
       <c r="Q96">
-        <v>-1.405805462399999</v>
+        <v>-1.541558712</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>1.340009866869012</v>
+        <v>1.598851840242816</v>
       </c>
       <c r="T96">
-        <v>7.915226436416192</v>
+        <v>9.498271723699435</v>
       </c>
       <c r="U96">
         <v>0.2008</v>
       </c>
       <c r="V96">
-        <v>0.1694211236406851</v>
+        <v>0.1676377433918357</v>
       </c>
       <c r="W96">
-        <v>0.1667802383729504</v>
+        <v>0.1671383411269194</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9197,7 +9197,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.5842107711747762</v>
+        <v>0.5780611841097785</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9205,22 +9205,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2387240160827141</v>
+        <v>0.2402740160827141</v>
       </c>
       <c r="C97">
-        <v>-38.96280767649767</v>
+        <v>-40.24685714102449</v>
       </c>
       <c r="D97">
-        <v>41.63619232350234</v>
+        <v>41.30434285897552</v>
       </c>
       <c r="E97">
-        <v>85.239</v>
+        <v>86.19120000000001</v>
       </c>
       <c r="F97">
-        <v>90.459</v>
+        <v>91.41120000000001</v>
       </c>
       <c r="G97">
         <v>9.859999999999999</v>
@@ -9241,37 +9241,37 @@
         <v>10.5</v>
       </c>
       <c r="M97">
-        <v>18.1641672</v>
+        <v>18.35536896</v>
       </c>
       <c r="N97">
-        <v>-7.664167200000001</v>
+        <v>-7.855368960000003</v>
       </c>
       <c r="O97">
-        <v>-2.222608488</v>
+        <v>-2.278056998400001</v>
       </c>
       <c r="P97">
-        <v>-5.441558712000001</v>
+        <v>-5.577311961600003</v>
       </c>
       <c r="Q97">
-        <v>-1.541558712</v>
+        <v>-1.677311961600003</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>1.598851840242816</v>
+        <v>1.987114800303521</v>
       </c>
       <c r="T97">
-        <v>9.498271723699435</v>
+        <v>11.8728396546243</v>
       </c>
       <c r="U97">
         <v>0.2008</v>
       </c>
       <c r="V97">
-        <v>0.1676377433918357</v>
+        <v>0.1658915168981708</v>
       </c>
       <c r="W97">
-        <v>0.1671383411269194</v>
+        <v>0.1674889834068473</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9279,7 +9279,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.5780611841097785</v>
+        <v>0.5720397134419681</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9287,22 +9287,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2402740160827141</v>
+        <v>0.2418240160827141</v>
       </c>
       <c r="C98">
-        <v>-40.24685714102448</v>
+        <v>-41.52565860910376</v>
       </c>
       <c r="D98">
-        <v>41.30434285897552</v>
+        <v>40.97774139089623</v>
       </c>
       <c r="E98">
-        <v>86.19119999999999</v>
+        <v>87.1434</v>
       </c>
       <c r="F98">
-        <v>91.41119999999999</v>
+        <v>92.3634</v>
       </c>
       <c r="G98">
         <v>9.859999999999999</v>
@@ -9323,37 +9323,37 @@
         <v>10.5</v>
       </c>
       <c r="M98">
-        <v>18.35536896</v>
+        <v>18.54657072</v>
       </c>
       <c r="N98">
-        <v>-7.85536896</v>
+        <v>-8.046570720000002</v>
       </c>
       <c r="O98">
-        <v>-2.2780569984</v>
+        <v>-2.333505508800001</v>
       </c>
       <c r="P98">
-        <v>-5.5773119616</v>
+        <v>-5.713065211200002</v>
       </c>
       <c r="Q98">
-        <v>-1.677311961599999</v>
+        <v>-1.813065211200001</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.987114800303515</v>
+        <v>2.63421973373802</v>
       </c>
       <c r="T98">
-        <v>11.87283965462427</v>
+        <v>15.83045287283236</v>
       </c>
       <c r="U98">
         <v>0.2008</v>
       </c>
       <c r="V98">
-        <v>0.1658915168981708</v>
+        <v>0.1641812950744783</v>
       </c>
       <c r="W98">
-        <v>0.1674889834068473</v>
+        <v>0.1678323959490448</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9361,7 +9361,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.5720397134419684</v>
+        <v>0.5661423968085459</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9369,22 +9369,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2418240160827141</v>
+        <v>0.2433740160827141</v>
       </c>
       <c r="C99">
-        <v>-41.52565860910376</v>
+        <v>-42.79933559486944</v>
       </c>
       <c r="D99">
-        <v>40.97774139089623</v>
+        <v>40.65626440513056</v>
       </c>
       <c r="E99">
-        <v>87.1434</v>
+        <v>88.0956</v>
       </c>
       <c r="F99">
-        <v>92.3634</v>
+        <v>93.3156</v>
       </c>
       <c r="G99">
         <v>9.859999999999999</v>
@@ -9405,37 +9405,37 @@
         <v>10.5</v>
       </c>
       <c r="M99">
-        <v>18.54657072</v>
+        <v>18.73777248</v>
       </c>
       <c r="N99">
-        <v>-8.046570720000002</v>
+        <v>-8.23777248</v>
       </c>
       <c r="O99">
-        <v>-2.333505508800001</v>
+        <v>-2.3889540192</v>
       </c>
       <c r="P99">
-        <v>-5.713065211200002</v>
+        <v>-5.8488184608</v>
       </c>
       <c r="Q99">
-        <v>-1.813065211200001</v>
+        <v>-1.9488184608</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>2.63421973373802</v>
+        <v>3.92842960060703</v>
       </c>
       <c r="T99">
-        <v>15.83045287283236</v>
+        <v>23.74567930924853</v>
       </c>
       <c r="U99">
         <v>0.2008</v>
       </c>
       <c r="V99">
-        <v>0.1641812950744783</v>
+        <v>0.1625059757369836</v>
       </c>
       <c r="W99">
-        <v>0.1678323959490448</v>
+        <v>0.1681688000720137</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9443,7 +9443,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.5661423968085459</v>
+        <v>0.5603654335758057</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9451,22 +9451,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2433740160827141</v>
+        <v>0.2449240160827141</v>
       </c>
       <c r="C100">
-        <v>-42.79933559486944</v>
+        <v>-44.06800776667303</v>
       </c>
       <c r="D100">
-        <v>40.65626440513056</v>
+        <v>40.33979223332696</v>
       </c>
       <c r="E100">
-        <v>88.0956</v>
+        <v>89.0478</v>
       </c>
       <c r="F100">
-        <v>93.3156</v>
+        <v>94.26779999999999</v>
       </c>
       <c r="G100">
         <v>9.859999999999999</v>
@@ -9487,37 +9487,37 @@
         <v>10.5</v>
       </c>
       <c r="M100">
-        <v>18.73777248</v>
+        <v>18.92897424</v>
       </c>
       <c r="N100">
-        <v>-8.23777248</v>
+        <v>-8.428974239999999</v>
       </c>
       <c r="O100">
-        <v>-2.3889540192</v>
+        <v>-2.4444025296</v>
       </c>
       <c r="P100">
-        <v>-5.8488184608</v>
+        <v>-5.984571710399999</v>
       </c>
       <c r="Q100">
-        <v>-1.9488184608</v>
+        <v>-2.084571710399999</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>3.92842960060703</v>
+        <v>7.811059201214061</v>
       </c>
       <c r="T100">
-        <v>23.74567930924853</v>
+        <v>47.49135861849707</v>
       </c>
       <c r="U100">
         <v>0.2008</v>
       </c>
       <c r="V100">
-        <v>0.1625059757369836</v>
+        <v>0.1608645012345899</v>
       </c>
       <c r="W100">
-        <v>0.1681688000720137</v>
+        <v>0.1684984081520944</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9525,91 +9525,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.5603654335758057</v>
+        <v>0.5547051766709996</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2449240160827141</v>
-      </c>
-      <c r="C101">
-        <v>-44.06800776667303</v>
-      </c>
-      <c r="D101">
-        <v>40.33979223332696</v>
-      </c>
-      <c r="E101">
-        <v>89.0478</v>
-      </c>
-      <c r="F101">
-        <v>94.26779999999999</v>
-      </c>
-      <c r="G101">
-        <v>9.859999999999999</v>
-      </c>
-      <c r="H101">
-        <v>90</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>14.4</v>
-      </c>
-      <c r="K101">
-        <v>3.9</v>
-      </c>
-      <c r="L101">
-        <v>10.5</v>
-      </c>
-      <c r="M101">
-        <v>18.92897424</v>
-      </c>
-      <c r="N101">
-        <v>-8.428974239999999</v>
-      </c>
-      <c r="O101">
-        <v>-2.4444025296</v>
-      </c>
-      <c r="P101">
-        <v>-5.984571710399999</v>
-      </c>
-      <c r="Q101">
-        <v>-2.084571710399999</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>7.811059201214061</v>
-      </c>
-      <c r="T101">
-        <v>47.49135861849707</v>
-      </c>
-      <c r="U101">
-        <v>0.2008</v>
-      </c>
-      <c r="V101">
-        <v>0.1608645012345899</v>
-      </c>
-      <c r="W101">
-        <v>0.1684984081520944</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>C2/C</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.5547051766709996</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
